--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,14 +851,14 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -873,317 +873,317 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L14" s="15">
         <v>-85.714285714285</v>
       </c>
       <c r="M14" s="15">
-        <v>-90</v>
+        <v>-91.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-96.666666666666</v>
+        <v>-97.222222222222</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>75</v>
+        <v>-40</v>
       </c>
       <c r="F15" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G15" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J15" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K15" s="15">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="L15" s="15">
-        <v>26.315789473684</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M15" s="15">
-        <v>118.181818181818</v>
+        <v>92.857142857142</v>
       </c>
       <c r="N15" s="15">
-        <v>-55.555555555555</v>
+        <v>-56.451612903225</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D16" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E16" s="15">
-        <v>-32.142857142857</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="F16" s="14">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G16" s="14">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H16" s="15">
-        <v>-2.884615384615</v>
+        <v>-16.379310344827</v>
       </c>
       <c r="I16" s="14">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="J16" s="14">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.974358974358</v>
+        <v>-7.936507936507</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.444933920704</v>
+        <v>-36.029411764705</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.202749140893</v>
+        <v>-49.565217391304</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.196528208307</v>
+        <v>-90.724946695096</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D17" s="14">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="F17" s="14">
         <v>252</v>
       </c>
       <c r="G17" s="14">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="H17" s="15">
-        <v>21.153846153846</v>
+        <v>14.545454545454</v>
       </c>
       <c r="I17" s="14">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="J17" s="14">
-        <v>318</v>
+        <v>385</v>
       </c>
       <c r="K17" s="15">
-        <v>6.289308176100</v>
+        <v>4.935064935064</v>
       </c>
       <c r="L17" s="15">
-        <v>6.962025316455</v>
+        <v>1.507537688442</v>
       </c>
       <c r="M17" s="15">
-        <v>65.686274509803</v>
+        <v>77.973568281938</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.771241830065</v>
+        <v>-44.198895027624</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D18" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E18" s="15">
-        <v>-19.047619047619</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G18" s="14">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H18" s="15">
-        <v>-39.024390243902</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="I18" s="14">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="J18" s="14">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.625</v>
+        <v>-28.191489361702</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.288135593220</v>
+        <v>-33.497536945812</v>
       </c>
       <c r="M18" s="15">
-        <v>-71.391752577319</v>
+        <v>-68.085106382978</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.898897058823</v>
+        <v>-94.632206759443</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
         <v>82</v>
       </c>
       <c r="D19" s="14">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.811881188118</v>
+        <v>18.840579710144</v>
       </c>
       <c r="F19" s="14">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G19" s="14">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.897506925207</v>
+        <v>-14</v>
       </c>
       <c r="I19" s="14">
-        <v>420</v>
+        <v>502</v>
       </c>
       <c r="J19" s="14">
-        <v>482</v>
+        <v>551</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.863070539419</v>
+        <v>-8.892921960072</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.121019108280</v>
+        <v>-32.707774798927</v>
       </c>
       <c r="M19" s="15">
-        <v>-27.835051546391</v>
+        <v>-24.283559577677</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.646298472385</v>
+        <v>-49.395161290322</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D20" s="14">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E20" s="15">
-        <v>18.518518518518</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F20" s="14">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="G20" s="14">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H20" s="15">
-        <v>23.076923076923</v>
+        <v>19.266055045871</v>
       </c>
       <c r="I20" s="14">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="J20" s="14">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="K20" s="15">
-        <v>10.791366906474</v>
+        <v>11.299435028248</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-26.217228464419</v>
       </c>
       <c r="M20" s="15">
-        <v>-33.333333333333</v>
+        <v>-21.513944223107</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.292068198665</v>
+        <v>-93.677792041078</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="D21" s="17">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.745762711864</v>
+        <v>-0.414937759336</v>
       </c>
       <c r="F21" s="17">
-        <v>859</v>
+        <v>877</v>
       </c>
       <c r="G21" s="17">
-        <v>908</v>
+        <v>931</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.396475770925</v>
+        <v>-5.800214822771</v>
       </c>
       <c r="I21" s="17">
-        <v>1190</v>
+        <v>1440</v>
       </c>
       <c r="J21" s="17">
-        <v>1285</v>
+        <v>1526</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.392996108949</v>
+        <v>-5.635648754914</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.856697819314</v>
+        <v>-24.764890282131</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.693069306930</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.187951207368</v>
+        <v>-84.551013839716</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
         <v>100</v>
@@ -1192,28 +1192,28 @@
         <v>15</v>
       </c>
       <c r="G22" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H22" s="15">
-        <v>7.142857142857</v>
+        <v>25</v>
       </c>
       <c r="I22" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J22" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>31.25</v>
+        <v>38.888888888888</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="M22" s="15">
-        <v>-32.258064516129</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G23" s="14">
+        <v>30</v>
+      </c>
+      <c r="H23" s="15">
+        <v>26.666666666666</v>
+      </c>
+      <c r="I23" s="14">
+        <v>64</v>
+      </c>
+      <c r="J23" s="14">
+        <v>50</v>
+      </c>
+      <c r="K23" s="15">
+        <v>28</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-20.987654320987</v>
+      </c>
+      <c r="M23" s="15">
+        <v>106.451612903226</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="H23" s="15">
-        <v>51.724137931034</v>
-      </c>
-      <c r="I23" s="14">
-        <v>57</v>
-      </c>
-      <c r="J23" s="14">
-        <v>43</v>
-      </c>
-      <c r="K23" s="15">
-        <v>32.558139534883</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-21.917808219178</v>
-      </c>
-      <c r="M23" s="15">
-        <v>103.571428571429</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D24" s="14">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="E24" s="15">
-        <v>-31.292517006802</v>
+        <v>-8.974358974358</v>
       </c>
       <c r="F24" s="14">
-        <v>866</v>
+        <v>843</v>
       </c>
       <c r="G24" s="14">
-        <v>1079</v>
+        <v>1022</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.740500463392</v>
+        <v>-17.514677103718</v>
       </c>
       <c r="I24" s="14">
-        <v>1236</v>
+        <v>1452</v>
       </c>
       <c r="J24" s="14">
-        <v>1447</v>
+        <v>1681</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.581893572909</v>
+        <v>-13.622843545508</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.556390977443</v>
+        <v>-22.103004291845</v>
       </c>
       <c r="M24" s="15">
-        <v>-6.150341685649</v>
+        <v>-1.157249829816</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D25" s="14">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="E25" s="15">
-        <v>-30.232558139534</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F25" s="14">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="G25" s="14">
-        <v>504</v>
+        <v>475</v>
       </c>
       <c r="H25" s="15">
-        <v>-26.388888888888</v>
+        <v>-23.789473684210</v>
       </c>
       <c r="I25" s="14">
-        <v>503</v>
+        <v>576</v>
       </c>
       <c r="J25" s="14">
-        <v>677</v>
+        <v>779</v>
       </c>
       <c r="K25" s="15">
-        <v>-25.701624815361</v>
+        <v>-26.059050064184</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.027027027027</v>
+        <v>-33.256083429895</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D26" s="14">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E26" s="15">
-        <v>7</v>
+        <v>25.806451612903</v>
       </c>
       <c r="F26" s="14">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="G26" s="14">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H26" s="15">
-        <v>12.5</v>
+        <v>16.363636363636</v>
       </c>
       <c r="I26" s="14">
-        <v>612</v>
+        <v>728</v>
       </c>
       <c r="J26" s="14">
-        <v>567</v>
+        <v>660</v>
       </c>
       <c r="K26" s="15">
-        <v>7.936507936507</v>
+        <v>10.303030303030</v>
       </c>
       <c r="L26" s="15">
-        <v>0.327868852459</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.108108108108</v>
+        <v>-4.461942257217</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>16.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F27" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G27" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J27" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K27" s="15">
-        <v>-9.677419354838</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>-9.677419354838</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,163 +1426,163 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E28" s="15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G28" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H28" s="15">
-        <v>12.765957446808</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I28" s="14">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J28" s="14">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K28" s="15">
-        <v>-1.408450704225</v>
+        <v>12.048192771084</v>
       </c>
       <c r="L28" s="15">
-        <v>-12.5</v>
+        <v>3.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>-87.5</v>
+        <v>-75</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>-72.727272727272</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-72.727272727272</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.25</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.890410958904</v>
+        <v>-95.505617977528</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>7</v>
       </c>
       <c r="H30" s="15">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>-80</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="M30" s="15">
-        <v>-85.714285714285</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.969696969697</v>
+        <v>-96.202531645569</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
       <c r="E31" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>33.333333333333</v>
+        <v>175</v>
       </c>
       <c r="I31" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J31" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31" s="15">
-        <v>55.555555555555</v>
+        <v>70</v>
       </c>
       <c r="L31" s="15">
-        <v>55.555555555555</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,20 +1607,20 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
+        <v>1</v>
+      </c>
+      <c r="G33" s="14">
         <v>2</v>
-      </c>
-      <c r="G33" s="14">
-        <v>4</v>
       </c>
       <c r="H33" s="15">
         <v>-50</v>
@@ -1638,10 +1638,10 @@
         <v>-57.142857142857</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>446</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>15832</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>6359</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>24308</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>10688</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>32462</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>90355</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -854,366 +854,366 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>6</v>
       </c>
       <c r="K14" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="L14" s="15">
+        <v>-75</v>
+      </c>
+      <c r="M14" s="15">
         <v>-83.333333333333</v>
       </c>
-      <c r="L14" s="15">
-        <v>-85.714285714285</v>
-      </c>
-      <c r="M14" s="15">
-        <v>-91.666666666666</v>
-      </c>
       <c r="N14" s="15">
-        <v>-97.222222222222</v>
+        <v>-94.871794871794</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>4</v>
+      </c>
+      <c r="D15" s="14">
+        <v>9</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="F15" s="14">
+        <v>17</v>
+      </c>
+      <c r="G15" s="14">
         <v>21</v>
       </c>
-      <c r="C15" s="14">
-        <v>3</v>
-      </c>
-      <c r="D15" s="14">
-        <v>5</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-40</v>
-      </c>
-      <c r="F15" s="14">
-        <v>16</v>
-      </c>
-      <c r="G15" s="14">
-        <v>16</v>
-      </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I15" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J15" s="14">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K15" s="15">
-        <v>-10</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="L15" s="15">
-        <v>28.571428571428</v>
+        <v>19.230769230769</v>
       </c>
       <c r="M15" s="15">
-        <v>92.857142857142</v>
+        <v>93.75</v>
       </c>
       <c r="N15" s="15">
-        <v>-56.451612903225</v>
+        <v>-59.210526315789</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="15">
-        <v>-12.121212121212</v>
+        <v>-12.5</v>
       </c>
       <c r="F16" s="14">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="G16" s="14">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.379310344827</v>
+        <v>-8.403361344537</v>
       </c>
       <c r="I16" s="14">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="J16" s="14">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.936507936507</v>
+        <v>-7.239819004524</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.029411764705</v>
+        <v>-33.224755700325</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.565217391304</v>
+        <v>-48.492462311557</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.724946695096</v>
+        <v>-90.478402229447</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D17" s="14">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E17" s="15">
-        <v>-5.970149253731</v>
+        <v>37.037037037037</v>
       </c>
       <c r="F17" s="14">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="G17" s="14">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="H17" s="15">
-        <v>14.545454545454</v>
+        <v>12.133891213389</v>
       </c>
       <c r="I17" s="14">
-        <v>404</v>
+        <v>479</v>
       </c>
       <c r="J17" s="14">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="K17" s="15">
-        <v>4.935064935064</v>
+        <v>9.111617312072</v>
       </c>
       <c r="L17" s="15">
-        <v>1.507537688442</v>
+        <v>3.904555314533</v>
       </c>
       <c r="M17" s="15">
-        <v>77.973568281938</v>
+        <v>76.752767527675</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.198895027624</v>
+        <v>-42.009685230024</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18" s="14">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G18" s="14">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H18" s="15">
-        <v>-31.034482758620</v>
+        <v>-25.471698113207</v>
       </c>
       <c r="I18" s="14">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="J18" s="14">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.191489361702</v>
+        <v>-24.637681159420</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.497536945812</v>
+        <v>-32.467532467532</v>
       </c>
       <c r="M18" s="15">
-        <v>-68.085106382978</v>
+        <v>-67.157894736842</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.632206759443</v>
+        <v>-94.566353187042</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D19" s="14">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E19" s="15">
-        <v>18.840579710144</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="F19" s="14">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="G19" s="14">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="H19" s="15">
-        <v>-14</v>
+        <v>-11.388888888888</v>
       </c>
       <c r="I19" s="14">
-        <v>502</v>
+        <v>593</v>
       </c>
       <c r="J19" s="14">
-        <v>551</v>
+        <v>643</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.892921960072</v>
+        <v>-7.776049766718</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.707774798927</v>
+        <v>-29.905437352245</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.283559577677</v>
+        <v>-20.295698924731</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.395161290322</v>
+        <v>-48.344947735191</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D20" s="14">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E20" s="15">
-        <v>10.526315789473</v>
+        <v>63.157894736842</v>
       </c>
       <c r="F20" s="14">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G20" s="14">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H20" s="15">
-        <v>19.266055045871</v>
+        <v>12.727272727272</v>
       </c>
       <c r="I20" s="14">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="J20" s="14">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K20" s="15">
-        <v>11.299435028248</v>
+        <v>16.836734693877</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.217228464419</v>
+        <v>-22.372881355932</v>
       </c>
       <c r="M20" s="15">
-        <v>-21.513944223107</v>
+        <v>-21.575342465753</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.677792041078</v>
+        <v>-93.576437587657</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D21" s="17">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E21" s="18">
-        <v>-0.414937759336</v>
+        <v>9.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>877</v>
+        <v>918</v>
       </c>
       <c r="G21" s="17">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.800214822771</v>
+        <v>-4.175365344467</v>
       </c>
       <c r="I21" s="17">
-        <v>1440</v>
+        <v>1695</v>
       </c>
       <c r="J21" s="17">
-        <v>1526</v>
+        <v>1751</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.635648754914</v>
+        <v>-3.198172472872</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.764890282131</v>
+        <v>-22.033118675253</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.581395348837</v>
+        <v>-23.233695652173</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.551013839716</v>
+        <v>-84.126240869076</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H22" s="15">
-        <v>25</v>
+        <v>77.777777777777</v>
       </c>
       <c r="I22" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J22" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K22" s="15">
-        <v>38.888888888888</v>
+        <v>35</v>
       </c>
       <c r="L22" s="15">
-        <v>-3.846153846153</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="M22" s="15">
-        <v>-24.242424242424</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F23" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G23" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H23" s="15">
-        <v>26.666666666666</v>
+        <v>24.242424242424</v>
       </c>
       <c r="I23" s="14">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J23" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K23" s="15">
-        <v>28</v>
+        <v>27.118644067796</v>
       </c>
       <c r="L23" s="15">
-        <v>-20.987654320987</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>106.451612903226</v>
+        <v>92.307692307692</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="D24" s="14">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="E24" s="15">
-        <v>-8.974358974358</v>
+        <v>-39.160839160839</v>
       </c>
       <c r="F24" s="14">
-        <v>843</v>
+        <v>771</v>
       </c>
       <c r="G24" s="14">
-        <v>1022</v>
+        <v>1065</v>
       </c>
       <c r="H24" s="15">
-        <v>-17.514677103718</v>
+        <v>-27.605633802816</v>
       </c>
       <c r="I24" s="14">
-        <v>1452</v>
+        <v>1624</v>
       </c>
       <c r="J24" s="14">
-        <v>1681</v>
+        <v>1967</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.622843545508</v>
+        <v>-17.437722419928</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.103004291845</v>
+        <v>-24.394785847299</v>
       </c>
       <c r="M24" s="15">
-        <v>-1.157249829816</v>
+        <v>-2.637889688249</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D25" s="14">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="E25" s="15">
-        <v>-29.411764705882</v>
+        <v>-53.488372093023</v>
       </c>
       <c r="F25" s="14">
-        <v>362</v>
+        <v>315</v>
       </c>
       <c r="G25" s="14">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.789473684210</v>
+        <v>-33.262711864406</v>
       </c>
       <c r="I25" s="14">
-        <v>576</v>
+        <v>637</v>
       </c>
       <c r="J25" s="14">
-        <v>779</v>
+        <v>908</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.059050064184</v>
+        <v>-29.845814977973</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.256083429895</v>
+        <v>-36.930693069306</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="D26" s="14">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E26" s="15">
-        <v>25.806451612903</v>
+        <v>39.393939393939</v>
       </c>
       <c r="F26" s="14">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="G26" s="14">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H26" s="15">
-        <v>16.363636363636</v>
+        <v>23.589743589743</v>
       </c>
       <c r="I26" s="14">
-        <v>728</v>
+        <v>865</v>
       </c>
       <c r="J26" s="14">
-        <v>660</v>
+        <v>759</v>
       </c>
       <c r="K26" s="15">
-        <v>10.303030303030</v>
+        <v>13.965744400527</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>4.468599033816</v>
       </c>
       <c r="M26" s="15">
-        <v>-4.461942257217</v>
+        <v>0.933488914819</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E27" s="15">
-        <v>-40</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F27" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="I27" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J27" s="14">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K27" s="15">
-        <v>-11.111111111111</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="L27" s="15">
-        <v>-5.882352941176</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D28" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F28" s="14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G28" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H28" s="15">
-        <v>45.454545454545</v>
+        <v>48.888888888888</v>
       </c>
       <c r="I28" s="14">
+        <v>106</v>
+      </c>
+      <c r="J28" s="14">
         <v>93</v>
       </c>
-      <c r="J28" s="14">
-        <v>83</v>
-      </c>
       <c r="K28" s="15">
-        <v>12.048192771084</v>
+        <v>13.978494623655</v>
       </c>
       <c r="L28" s="15">
-        <v>3.333333333333</v>
+        <v>6</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J29" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="15">
-        <v>-66.666666666666</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.505617977528</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
+        <v>500</v>
+      </c>
+      <c r="F30" s="14">
+        <v>8</v>
+      </c>
+      <c r="G30" s="14">
+        <v>8</v>
+      </c>
+      <c r="H30" s="15">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="14">
-        <v>7</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-71.428571428571</v>
-      </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K30" s="15">
-        <v>-72.727272727272</v>
+        <v>-25</v>
       </c>
       <c r="L30" s="15">
-        <v>-72.727272727272</v>
+        <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-83.333333333333</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.202531645569</v>
+        <v>-90.425531914893</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G31" s="14">
         <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="I31" s="14">
         <v>17</v>
@@ -1576,13 +1576,13 @@
         <v>70</v>
       </c>
       <c r="L31" s="15">
-        <v>30.769230769230</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>3</v>
@@ -1638,10 +1638,10 @@
         <v>-57.142857142857</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>446</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>15832</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>6359</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>24308</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>10688</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>32462</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>90355</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -864,10 +864,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -879,13 +879,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M14" s="15">
         <v>-83.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-94.871794871794</v>
+        <v>-95.348837209302</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>4</v>
       </c>
       <c r="D15" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15" s="15">
-        <v>-55.555555555555</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H15" s="15">
-        <v>-19.047619047619</v>
+        <v>-28</v>
       </c>
       <c r="I15" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J15" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K15" s="15">
-        <v>-20.512820512820</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="L15" s="15">
-        <v>19.230769230769</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>93.75</v>
+        <v>84.210526315789</v>
       </c>
       <c r="N15" s="15">
-        <v>-59.210526315789</v>
+        <v>-58.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>19</v>
+      </c>
+      <c r="D16" s="14">
         <v>28</v>
       </c>
-      <c r="D16" s="14">
-        <v>32</v>
-      </c>
       <c r="E16" s="15">
-        <v>-12.5</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G16" s="14">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H16" s="15">
-        <v>-8.403361344537</v>
+        <v>-19.008264462809</v>
       </c>
       <c r="I16" s="14">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="J16" s="14">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.239819004524</v>
+        <v>-10.040160642570</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.224755700325</v>
+        <v>-32.732732732732</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.492462311557</v>
+        <v>-49.321266968325</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.478402229447</v>
+        <v>-90.868324500611</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" s="14">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E17" s="15">
-        <v>37.037037037037</v>
+        <v>19.672131147541</v>
       </c>
       <c r="F17" s="14">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G17" s="14">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H17" s="15">
-        <v>12.133891213389</v>
+        <v>12.658227848101</v>
       </c>
       <c r="I17" s="14">
-        <v>479</v>
+        <v>553</v>
       </c>
       <c r="J17" s="14">
-        <v>439</v>
+        <v>500</v>
       </c>
       <c r="K17" s="15">
-        <v>9.111617312072</v>
+        <v>10.6</v>
       </c>
       <c r="L17" s="15">
-        <v>3.904555314533</v>
+        <v>5.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>76.752767527675</v>
+        <v>75.555555555555</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.009685230024</v>
+        <v>-39.096916299559</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D18" s="14">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="F18" s="14">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G18" s="14">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H18" s="15">
-        <v>-25.471698113207</v>
+        <v>-8.080808080808</v>
       </c>
       <c r="I18" s="14">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="J18" s="14">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="K18" s="15">
-        <v>-24.637681159420</v>
+        <v>-21.848739495798</v>
       </c>
       <c r="L18" s="15">
-        <v>-32.467532467532</v>
+        <v>-28.185328185328</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.157894736842</v>
+        <v>-64.839319470699</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.566353187042</v>
+        <v>-94.216417910447</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D19" s="14">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E19" s="15">
-        <v>-2.173913043478</v>
+        <v>-21.774193548387</v>
       </c>
       <c r="F19" s="14">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="G19" s="14">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.388888888888</v>
+        <v>-9.585492227979</v>
       </c>
       <c r="I19" s="14">
-        <v>593</v>
+        <v>687</v>
       </c>
       <c r="J19" s="14">
-        <v>643</v>
+        <v>767</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.776049766718</v>
+        <v>-10.430247718383</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.905437352245</v>
+        <v>-29.897959183673</v>
       </c>
       <c r="M19" s="15">
-        <v>-20.295698924731</v>
+        <v>-17.527010804321</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.344947735191</v>
+        <v>-47.356321839080</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D20" s="14">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E20" s="15">
-        <v>63.157894736842</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="F20" s="14">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G20" s="14">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H20" s="15">
-        <v>12.727272727272</v>
+        <v>12.389380530973</v>
       </c>
       <c r="I20" s="14">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="J20" s="14">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="K20" s="15">
-        <v>16.836734693877</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.372881355932</v>
+        <v>-22.360248447205</v>
       </c>
       <c r="M20" s="15">
-        <v>-21.575342465753</v>
+        <v>-21.135646687697</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.576437587657</v>
+        <v>-93.751562109472</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D21" s="17">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="E21" s="18">
-        <v>9.333333333333</v>
+        <v>-12.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>918</v>
+        <v>952</v>
       </c>
       <c r="G21" s="17">
-        <v>958</v>
+        <v>982</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.175365344467</v>
+        <v>-3.054989816700</v>
       </c>
       <c r="I21" s="17">
-        <v>1695</v>
+        <v>1937</v>
       </c>
       <c r="J21" s="17">
-        <v>1751</v>
+        <v>2031</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.198172472872</v>
+        <v>-4.628261939931</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.033118675253</v>
+        <v>-21.196094385679</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.233695652173</v>
+        <v>-21.483583299554</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.126240869076</v>
+        <v>-83.871773522064</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-50</v>
+        <v>7</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G22" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>77.777777777777</v>
+        <v>171.428571428571</v>
       </c>
       <c r="I22" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J22" s="14">
         <v>20</v>
       </c>
       <c r="K22" s="15">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L22" s="15">
-        <v>-3.571428571428</v>
+        <v>17.241379310344</v>
       </c>
       <c r="M22" s="15">
-        <v>-22.857142857142</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="F23" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G23" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>24.242424242424</v>
+        <v>22.580645161290</v>
       </c>
       <c r="I23" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J23" s="14">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K23" s="15">
-        <v>27.118644067796</v>
+        <v>18.840579710144</v>
       </c>
       <c r="L23" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.463917525773</v>
       </c>
       <c r="M23" s="15">
-        <v>92.307692307692</v>
+        <v>105</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D24" s="14">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E24" s="15">
-        <v>-39.160839160839</v>
+        <v>-38.566552901023</v>
       </c>
       <c r="F24" s="14">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="G24" s="14">
-        <v>1065</v>
+        <v>1107</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.605633802816</v>
+        <v>-30.713640469738</v>
       </c>
       <c r="I24" s="14">
-        <v>1624</v>
+        <v>1804</v>
       </c>
       <c r="J24" s="14">
-        <v>1967</v>
+        <v>2260</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.437722419928</v>
+        <v>-20.176991150442</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.394785847299</v>
+        <v>-26.845093268450</v>
       </c>
       <c r="M24" s="15">
-        <v>-2.637889688249</v>
+        <v>-2.275189599133</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D25" s="14">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E25" s="15">
-        <v>-53.488372093023</v>
+        <v>-48.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="G25" s="14">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="H25" s="15">
-        <v>-33.262711864406</v>
+        <v>-40.4</v>
       </c>
       <c r="I25" s="14">
-        <v>637</v>
+        <v>710</v>
       </c>
       <c r="J25" s="14">
-        <v>908</v>
+        <v>1048</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.845814977973</v>
+        <v>-32.251908396946</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.930693069306</v>
+        <v>-38.260869565217</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="D26" s="14">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="E26" s="15">
-        <v>39.393939393939</v>
+        <v>-15.037593984962</v>
       </c>
       <c r="F26" s="14">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="G26" s="14">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="H26" s="15">
-        <v>23.589743589743</v>
+        <v>11.529411764705</v>
       </c>
       <c r="I26" s="14">
-        <v>865</v>
+        <v>976</v>
       </c>
       <c r="J26" s="14">
-        <v>759</v>
+        <v>892</v>
       </c>
       <c r="K26" s="15">
-        <v>13.965744400527</v>
+        <v>9.417040358744</v>
       </c>
       <c r="L26" s="15">
-        <v>4.468599033816</v>
+        <v>0.826446280991</v>
       </c>
       <c r="M26" s="15">
-        <v>0.933488914819</v>
+        <v>3.389830508474</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E27" s="15">
-        <v>-54.545454545454</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G27" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H27" s="15">
-        <v>-24</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="I27" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J27" s="14">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K27" s="15">
-        <v>-21.276595744680</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="L27" s="15">
-        <v>-11.904761904761</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E28" s="15">
-        <v>60</v>
+        <v>-25</v>
       </c>
       <c r="F28" s="14">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G28" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H28" s="15">
-        <v>48.888888888888</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I28" s="14">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J28" s="14">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="K28" s="15">
-        <v>13.978494623655</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>6</v>
+        <v>-7.438016528925</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>6</v>
-      </c>
-      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>500</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G29" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-11.111111111111</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J29" s="14">
         <v>13</v>
       </c>
       <c r="K29" s="15">
-        <v>-23.076923076923</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L29" s="15">
-        <v>-23.076923076923</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M29" s="15">
-        <v>-52.380952380952</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.476190476190</v>
+        <v>-89.285714285714</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,75 +1508,75 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>6</v>
-      </c>
-      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>500</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>8</v>
       </c>
       <c r="G30" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I30" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J30" s="14">
         <v>12</v>
       </c>
       <c r="K30" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M30" s="15">
-        <v>-52.631578947368</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.425531914893</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14">
+        <v>6</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="I31" s="14">
+        <v>18</v>
+      </c>
+      <c r="J31" s="14">
+        <v>13</v>
+      </c>
+      <c r="K31" s="15">
+        <v>38.461538461538</v>
+      </c>
+      <c r="L31" s="15">
         <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
-        <v>7</v>
-      </c>
-      <c r="G31" s="14">
-        <v>4</v>
-      </c>
-      <c r="H31" s="15">
-        <v>75</v>
-      </c>
-      <c r="I31" s="14">
-        <v>17</v>
-      </c>
-      <c r="J31" s="14">
-        <v>10</v>
-      </c>
-      <c r="K31" s="15">
-        <v>70</v>
-      </c>
-      <c r="L31" s="15">
-        <v>21.428571428571</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>0</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>3</v>
@@ -1635,7 +1635,7 @@
         <v>-40</v>
       </c>
       <c r="L33" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -199,67 +199,67 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
+    <t>Traffic Statistics</t>
+  </si>
+  <si>
+    <t>Traffic Fatalities</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>Traffic Statistics</t>
-  </si>
-  <si>
-    <t>Traffic Fatalities</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,547 +851,547 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
       </c>
       <c r="F14" s="14">
         <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="L14" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L14" s="15">
-        <v>-77.777777777777</v>
-      </c>
       <c r="M14" s="15">
-        <v>-83.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.348837209302</v>
+        <v>-93.478260869565</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
         <v>4</v>
       </c>
       <c r="D15" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>-42.857142857142</v>
+        <v>-20</v>
       </c>
       <c r="F15" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G15" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" s="15">
-        <v>-28</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I15" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J15" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K15" s="15">
-        <v>-23.913043478260</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="L15" s="15">
-        <v>16.666666666666</v>
+        <v>17.647058823529</v>
       </c>
       <c r="M15" s="15">
-        <v>84.210526315789</v>
+        <v>73.913043478260</v>
       </c>
       <c r="N15" s="15">
-        <v>-58.333333333333</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D16" s="14">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E16" s="15">
-        <v>-32.142857142857</v>
+        <v>56.25</v>
       </c>
       <c r="F16" s="14">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G16" s="14">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H16" s="15">
-        <v>-19.008264462809</v>
+        <v>-4.587155963302</v>
       </c>
       <c r="I16" s="14">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="J16" s="14">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="K16" s="15">
-        <v>-10.040160642570</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.732732732732</v>
+        <v>-30.167597765363</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.321266968325</v>
+        <v>-49.392712550607</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.868324500611</v>
+        <v>-90.852542993047</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D17" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E17" s="15">
-        <v>19.672131147541</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="F17" s="14">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="G17" s="14">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="H17" s="15">
-        <v>12.658227848101</v>
+        <v>10.040160642570</v>
       </c>
       <c r="I17" s="14">
-        <v>553</v>
+        <v>619</v>
       </c>
       <c r="J17" s="14">
-        <v>500</v>
+        <v>567</v>
       </c>
       <c r="K17" s="15">
-        <v>10.6</v>
+        <v>9.171075837742</v>
       </c>
       <c r="L17" s="15">
-        <v>5.333333333333</v>
+        <v>5.631399317406</v>
       </c>
       <c r="M17" s="15">
-        <v>75.555555555555</v>
+        <v>73.876404494382</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.096916299559</v>
+        <v>-39.074803149606</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D18" s="14">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E18" s="15">
-        <v>-6.451612903225</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F18" s="14">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G18" s="14">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H18" s="15">
-        <v>-8.080808080808</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="I18" s="14">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="J18" s="14">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.848739495798</v>
+        <v>-22.348484848484</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.185328185328</v>
+        <v>-27.561837455830</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.839319470699</v>
+        <v>-65.371621621621</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.216417910447</v>
+        <v>-94.267337807606</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D19" s="14">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E19" s="15">
-        <v>-21.774193548387</v>
+        <v>-4.672897196261</v>
       </c>
       <c r="F19" s="14">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="G19" s="14">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.585492227979</v>
+        <v>-6.632653061224</v>
       </c>
       <c r="I19" s="14">
-        <v>687</v>
+        <v>788</v>
       </c>
       <c r="J19" s="14">
-        <v>767</v>
+        <v>874</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.430247718383</v>
+        <v>-9.839816933638</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.897959183673</v>
+        <v>-27.970749542961</v>
       </c>
       <c r="M19" s="15">
-        <v>-17.527010804321</v>
+        <v>-13.691128148959</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.356321839080</v>
+        <v>-46.138072453861</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>-24.137931034482</v>
+        <v>172.727272727273</v>
       </c>
       <c r="F20" s="14">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G20" s="14">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="H20" s="15">
-        <v>12.389380530973</v>
+        <v>28.865979381443</v>
       </c>
       <c r="I20" s="14">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="J20" s="14">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="K20" s="15">
-        <v>11.111111111111</v>
+        <v>17.796610169491</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.360248447205</v>
+        <v>-21.468926553672</v>
       </c>
       <c r="M20" s="15">
-        <v>-21.135646687697</v>
+        <v>-23.204419889502</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.751562109472</v>
+        <v>-93.797411869701</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D21" s="17">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.857142857142</v>
+        <v>3.433476394849</v>
       </c>
       <c r="F21" s="17">
-        <v>952</v>
+        <v>977</v>
       </c>
       <c r="G21" s="17">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.054989816700</v>
+        <v>-0.204290091930</v>
       </c>
       <c r="I21" s="17">
-        <v>1937</v>
+        <v>2183</v>
       </c>
       <c r="J21" s="17">
-        <v>2031</v>
+        <v>2264</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.628261939931</v>
+        <v>-3.577738515901</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.196094385679</v>
+        <v>-19.683590875643</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.483583299554</v>
+        <v>-20.675872093023</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.871773522064</v>
+        <v>-83.728384019081</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>7</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="14">
+        <v>4</v>
+      </c>
+      <c r="E22" s="15">
+        <v>150</v>
+      </c>
+      <c r="F22" s="14">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>19</v>
-      </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>171.428571428571</v>
+        <v>162.5</v>
       </c>
       <c r="I22" s="14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J22" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K22" s="15">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L22" s="15">
-        <v>17.241379310344</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M22" s="15">
-        <v>-17.073170731707</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
         <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H23" s="15">
-        <v>22.580645161290</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J23" s="14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="K23" s="15">
-        <v>18.840579710144</v>
+        <v>13.924050632911</v>
       </c>
       <c r="L23" s="15">
-        <v>-15.463917525773</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M23" s="15">
-        <v>105</v>
+        <v>104.545454545455</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="D24" s="14">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.566552901023</v>
+        <v>-13.553113553113</v>
       </c>
       <c r="F24" s="14">
-        <v>767</v>
+        <v>799</v>
       </c>
       <c r="G24" s="14">
-        <v>1107</v>
+        <v>1086</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.713640469738</v>
+        <v>-26.427255985267</v>
       </c>
       <c r="I24" s="14">
-        <v>1804</v>
+        <v>2038</v>
       </c>
       <c r="J24" s="14">
-        <v>2260</v>
+        <v>2533</v>
       </c>
       <c r="K24" s="15">
-        <v>-20.176991150442</v>
+        <v>-19.542045005921</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.845093268450</v>
+        <v>-24.434556915090</v>
       </c>
       <c r="M24" s="15">
-        <v>-2.275189599133</v>
+        <v>-0.146986771190</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="D25" s="14">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="E25" s="15">
-        <v>-48.571428571428</v>
+        <v>-29.365079365079</v>
       </c>
       <c r="F25" s="14">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G25" s="14">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H25" s="15">
-        <v>-40.4</v>
+        <v>-40.643863179074</v>
       </c>
       <c r="I25" s="14">
-        <v>710</v>
+        <v>799</v>
       </c>
       <c r="J25" s="14">
-        <v>1048</v>
+        <v>1174</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.251908396946</v>
+        <v>-31.942078364565</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.260869565217</v>
+        <v>-36.182108626198</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="D26" s="14">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.037593984962</v>
+        <v>24.770642201834</v>
       </c>
       <c r="F26" s="14">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="G26" s="14">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="H26" s="15">
-        <v>11.529411764705</v>
+        <v>15.207373271889</v>
       </c>
       <c r="I26" s="14">
-        <v>976</v>
+        <v>1106</v>
       </c>
       <c r="J26" s="14">
-        <v>892</v>
+        <v>1001</v>
       </c>
       <c r="K26" s="15">
-        <v>9.417040358744</v>
+        <v>10.489510489510</v>
       </c>
       <c r="L26" s="15">
-        <v>0.826446280991</v>
+        <v>1.841620626151</v>
       </c>
       <c r="M26" s="15">
-        <v>3.389830508474</v>
+        <v>3.558052434456</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
         <v>6</v>
       </c>
       <c r="D27" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>21</v>
@@ -1403,191 +1403,191 @@
         <v>-32.258064516129</v>
       </c>
       <c r="I27" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J27" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K27" s="15">
-        <v>-23.214285714285</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="L27" s="15">
-        <v>-15.686274509803</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D28" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>-25</v>
+        <v>18.75</v>
       </c>
       <c r="F28" s="14">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G28" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H28" s="15">
-        <v>45.454545454545</v>
+        <v>24</v>
       </c>
       <c r="I28" s="14">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="J28" s="14">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="K28" s="15">
-        <v>6.666666666666</v>
+        <v>5.737704918032</v>
       </c>
       <c r="L28" s="15">
-        <v>-7.438016528925</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
+        <v>6</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>500</v>
       </c>
       <c r="F29" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I29" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J29" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" s="15">
-        <v>-7.692307692307</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L29" s="15">
-        <v>-14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M29" s="15">
-        <v>-53.846153846153</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.285714285714</v>
+        <v>-85.365853658536</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
+        <v>3</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>200</v>
       </c>
       <c r="F30" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>166.666666666667</v>
+        <v>266.666666666667</v>
       </c>
       <c r="I30" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J30" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-23.076923076923</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-54.545454545454</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-88.181818181818</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="14">
+        <v>5</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-60</v>
+      </c>
+      <c r="F31" s="14">
         <v>3</v>
       </c>
-      <c r="E31" s="15">
+      <c r="G31" s="14">
+        <v>9</v>
+      </c>
+      <c r="H31" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
-      </c>
-      <c r="G31" s="14">
-        <v>6</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-83.333333333333</v>
-      </c>
       <c r="I31" s="14">
+        <v>19</v>
+      </c>
+      <c r="J31" s="14">
         <v>18</v>
       </c>
-      <c r="J31" s="14">
-        <v>13</v>
-      </c>
       <c r="K31" s="15">
-        <v>38.461538461538</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L31" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,43 +1605,43 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L33" s="15">
-        <v>-62.5</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>446</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>15832</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>6359</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>24308</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>10688</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>32462</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>90355</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -855,37 +855,37 @@
         <v>1</v>
       </c>
       <c r="D14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F14" s="14">
         <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K14" s="15">
-        <v>-57.142857142857</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L14" s="15">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M14" s="15">
-        <v>-75</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.478260869565</v>
+        <v>-91.489361702127</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E15" s="15">
-        <v>-20</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F15" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H15" s="15">
-        <v>-38.461538461538</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J15" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K15" s="15">
-        <v>-21.568627450980</v>
+        <v>-21.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>17.647058823529</v>
+        <v>20.512820512820</v>
       </c>
       <c r="M15" s="15">
-        <v>73.913043478260</v>
+        <v>74.074074074074</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-57.657657657657</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E16" s="15">
-        <v>56.25</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F16" s="14">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G16" s="14">
         <v>109</v>
       </c>
       <c r="H16" s="15">
-        <v>-4.587155963302</v>
+        <v>-6.422018348623</v>
       </c>
       <c r="I16" s="14">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="J16" s="14">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.660377358490</v>
+        <v>-6.375838926174</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.167597765363</v>
+        <v>-27.720207253886</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.392712550607</v>
+        <v>-48.994515539305</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.852542993047</v>
+        <v>-90.625</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D17" s="14">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E17" s="15">
-        <v>-8.955223880597</v>
+        <v>-28.75</v>
       </c>
       <c r="F17" s="14">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G17" s="14">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="H17" s="15">
-        <v>10.040160642570</v>
+        <v>2.671755725190</v>
       </c>
       <c r="I17" s="14">
-        <v>619</v>
+        <v>681</v>
       </c>
       <c r="J17" s="14">
-        <v>567</v>
+        <v>647</v>
       </c>
       <c r="K17" s="15">
-        <v>9.171075837742</v>
+        <v>5.255023183925</v>
       </c>
       <c r="L17" s="15">
-        <v>5.631399317406</v>
+        <v>3.495440729483</v>
       </c>
       <c r="M17" s="15">
-        <v>73.876404494382</v>
+        <v>70.676691729323</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.074803149606</v>
+        <v>-39.304812834224</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="15">
-        <v>-30.769230769230</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="14">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G18" s="14">
         <v>104</v>
       </c>
       <c r="H18" s="15">
-        <v>-13.461538461538</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="I18" s="14">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="J18" s="14">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.348484848484</v>
+        <v>-23.630136986301</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.561837455830</v>
+        <v>-27.361563517915</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.371621621621</v>
+        <v>-66.006097560975</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.267337807606</v>
+        <v>-94.243675787299</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D19" s="14">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E19" s="15">
-        <v>-4.672897196261</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="G19" s="14">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.632653061224</v>
+        <v>-4.976303317535</v>
       </c>
       <c r="I19" s="14">
-        <v>788</v>
+        <v>906</v>
       </c>
       <c r="J19" s="14">
-        <v>874</v>
+        <v>973</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.839816933638</v>
+        <v>-6.885919835560</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.970749542961</v>
+        <v>-25.185796862097</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.691128148959</v>
+        <v>-9.850746268656</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.138072453861</v>
+        <v>-43.691733996271</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E20" s="15">
-        <v>172.727272727273</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="F20" s="14">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G20" s="14">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H20" s="15">
-        <v>28.865979381443</v>
+        <v>21.739130434782</v>
       </c>
       <c r="I20" s="14">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="J20" s="14">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="K20" s="15">
-        <v>17.796610169491</v>
+        <v>13.754646840148</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.468926553672</v>
+        <v>-20.725388601036</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.204419889502</v>
+        <v>-24.257425742574</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.797411869701</v>
+        <v>-93.648816936488</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="D21" s="17">
-        <v>233</v>
+        <v>284</v>
       </c>
       <c r="E21" s="18">
-        <v>3.433476394849</v>
+        <v>-8.450704225352</v>
       </c>
       <c r="F21" s="17">
-        <v>977</v>
+        <v>990</v>
       </c>
       <c r="G21" s="17">
-        <v>979</v>
+        <v>1022</v>
       </c>
       <c r="H21" s="18">
-        <v>-0.204290091930</v>
+        <v>-3.131115459882</v>
       </c>
       <c r="I21" s="17">
-        <v>2183</v>
+        <v>2446</v>
       </c>
       <c r="J21" s="17">
-        <v>2264</v>
+        <v>2548</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.577738515901</v>
+        <v>-4.003139717425</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.683590875643</v>
+        <v>-18.357810413885</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.675872093023</v>
+        <v>-19.829564077351</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.728384019081</v>
+        <v>-83.197087311946</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" s="15">
-        <v>150</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F22" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H22" s="15">
-        <v>162.5</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J22" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K22" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>27.272727272727</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="15">
-        <v>-2.325581395348</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>28</v>
@@ -1230,28 +1230,28 @@
         <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G23" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H23" s="15">
-        <v>-8.333333333333</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I23" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J23" s="14">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K23" s="15">
-        <v>13.924050632911</v>
+        <v>5.617977528089</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.764705882352</v>
+        <v>-16.071428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>104.545454545455</v>
+        <v>88</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>28</v>
@@ -1262,37 +1262,37 @@
         <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="D24" s="14">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.553113553113</v>
+        <v>-5.985915492957</v>
       </c>
       <c r="F24" s="14">
-        <v>799</v>
+        <v>856</v>
       </c>
       <c r="G24" s="14">
-        <v>1086</v>
+        <v>1136</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.427255985267</v>
+        <v>-24.647887323943</v>
       </c>
       <c r="I24" s="14">
-        <v>2038</v>
+        <v>2303</v>
       </c>
       <c r="J24" s="14">
-        <v>2533</v>
+        <v>2817</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.542045005921</v>
+        <v>-18.246361377351</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.434556915090</v>
+        <v>-22.353337828725</v>
       </c>
       <c r="M24" s="15">
-        <v>-0.146986771190</v>
+        <v>3.042505592841</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>28</v>
@@ -1303,34 +1303,34 @@
         <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D25" s="14">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E25" s="15">
-        <v>-29.365079365079</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="F25" s="14">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G25" s="14">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="H25" s="15">
-        <v>-40.643863179074</v>
+        <v>-41.568627450980</v>
       </c>
       <c r="I25" s="14">
-        <v>799</v>
+        <v>876</v>
       </c>
       <c r="J25" s="14">
-        <v>1174</v>
+        <v>1289</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.942078364565</v>
+        <v>-32.040341349883</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.182108626198</v>
+        <v>-36.429608127721</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>28</v>
@@ -1344,37 +1344,37 @@
         <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D26" s="14">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="E26" s="15">
-        <v>24.770642201834</v>
+        <v>-4.477611940298</v>
       </c>
       <c r="F26" s="14">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="G26" s="14">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="H26" s="15">
-        <v>15.207373271889</v>
+        <v>9.684210526315</v>
       </c>
       <c r="I26" s="14">
-        <v>1106</v>
+        <v>1241</v>
       </c>
       <c r="J26" s="14">
-        <v>1001</v>
+        <v>1135</v>
       </c>
       <c r="K26" s="15">
-        <v>10.489510489510</v>
+        <v>9.339207048458</v>
       </c>
       <c r="L26" s="15">
-        <v>1.841620626151</v>
+        <v>2.308326463314</v>
       </c>
       <c r="M26" s="15">
-        <v>3.558052434456</v>
+        <v>3.330557868442</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>28</v>
@@ -1385,34 +1385,34 @@
         <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F27" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G27" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H27" s="15">
-        <v>-32.258064516129</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="I27" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J27" s="14">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="K27" s="15">
-        <v>-19.354838709677</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>-13.846153846153</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>28</v>
@@ -1426,34 +1426,34 @@
         <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D28" s="14">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>18.75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="G28" s="14">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H28" s="15">
-        <v>24</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I28" s="14">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="J28" s="14">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K28" s="15">
-        <v>5.737704918032</v>
+        <v>8.59375</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.521739130434</v>
+        <v>-4.794520547945</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>28</v>
@@ -1467,40 +1467,40 @@
         <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F29" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>400</v>
+        <v>466.666666666667</v>
       </c>
       <c r="I29" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J29" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" s="15">
-        <v>28.571428571428</v>
+        <v>40</v>
       </c>
       <c r="L29" s="15">
-        <v>28.571428571428</v>
+        <v>40</v>
       </c>
       <c r="M29" s="15">
-        <v>-30.769230769230</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.365853658536</v>
+        <v>-84.328358208955</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>266.666666666667</v>
+        <v>300</v>
       </c>
       <c r="I30" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J30" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M30" s="15">
-        <v>-40.909090909090</v>
+        <v>-40</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.181818181818</v>
+        <v>-87.603305785124</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,31 +1552,31 @@
         <v>2</v>
       </c>
       <c r="D31" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H31" s="15">
-        <v>-66.666666666666</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I31" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J31" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K31" s="15">
-        <v>5.555555555555</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>28</v>
@@ -1608,7 +1608,7 @@
         <v>39</v>
       </c>
       <c r="C33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>40</v>
@@ -1617,7 +1617,7 @@
         <v>28</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>40</v>
@@ -1626,16 +1626,16 @@
         <v>28</v>
       </c>
       <c r="I33" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L33" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>28</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,12 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
     <t>Transit</t>
   </si>
   <si>
-    <t>***.*</t>
-  </si>
-  <si>
     <t>Housing</t>
   </si>
   <si>
@@ -257,9 +260,6 @@
   </si>
   <si>
     <t>Traffic Fatalities</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -854,658 +854,658 @@
       <c r="C14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="14">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-50</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="14">
         <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="14">
         <v>9</v>
       </c>
       <c r="K14" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L14" s="15">
-        <v>-55.555555555555</v>
+        <v>-68.75</v>
       </c>
       <c r="M14" s="15">
-        <v>-69.230769230769</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.489361702127</v>
+        <v>-90.566037735849</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>-22.222222222222</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F15" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G15" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J15" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K15" s="15">
-        <v>-21.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>20.512820512820</v>
+        <v>36.585365853658</v>
       </c>
       <c r="M15" s="15">
-        <v>74.074074074074</v>
+        <v>86.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-57.657657657657</v>
+        <v>-52.136752136752</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D16" s="14">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E16" s="15">
-        <v>-9.090909090909</v>
+        <v>8.695652173913</v>
       </c>
       <c r="F16" s="14">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="14">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="H16" s="15">
-        <v>-6.422018348623</v>
+        <v>1</v>
       </c>
       <c r="I16" s="14">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="J16" s="14">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.375838926174</v>
+        <v>-4.361370716510</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.720207253886</v>
+        <v>-25.845410628019</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.994515539305</v>
+        <v>-48.576214405360</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.625</v>
+        <v>-90.559655596556</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D17" s="14">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.75</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="F17" s="14">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="G17" s="14">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="H17" s="15">
-        <v>2.671755725190</v>
+        <v>-5.434782608695</v>
       </c>
       <c r="I17" s="14">
-        <v>681</v>
+        <v>748</v>
       </c>
       <c r="J17" s="14">
-        <v>647</v>
+        <v>715</v>
       </c>
       <c r="K17" s="15">
-        <v>5.255023183925</v>
+        <v>4.615384615384</v>
       </c>
       <c r="L17" s="15">
-        <v>3.495440729483</v>
+        <v>3.744798890429</v>
       </c>
       <c r="M17" s="15">
-        <v>70.676691729323</v>
+        <v>65.486725663716</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.304812834224</v>
+        <v>-39.967897271268</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D18" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E18" s="15">
-        <v>-42.857142857142</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="F18" s="14">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G18" s="14">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.230769230769</v>
+        <v>-21.008403361344</v>
       </c>
       <c r="I18" s="14">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="J18" s="14">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="K18" s="15">
-        <v>-23.630136986301</v>
+        <v>-22.699386503067</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.361563517915</v>
+        <v>-24.776119402985</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.006097560975</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.243675787299</v>
+        <v>-93.984244449749</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D19" s="14">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E19" s="15">
-        <v>18.181818181818</v>
+        <v>-7.920792079207</v>
       </c>
       <c r="F19" s="14">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="G19" s="14">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.976303317535</v>
+        <v>-5.800464037122</v>
       </c>
       <c r="I19" s="14">
-        <v>906</v>
+        <v>996</v>
       </c>
       <c r="J19" s="14">
-        <v>973</v>
+        <v>1074</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.885919835560</v>
+        <v>-7.262569832402</v>
       </c>
       <c r="L19" s="15">
-        <v>-25.185796862097</v>
+        <v>-25.169045830202</v>
       </c>
       <c r="M19" s="15">
-        <v>-9.850746268656</v>
+        <v>-8.287292817679</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.691733996271</v>
+        <v>-43.247863247863</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="14">
         <v>33</v>
       </c>
       <c r="E20" s="15">
-        <v>-3.030303030303</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="F20" s="14">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G20" s="14">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H20" s="15">
-        <v>21.739130434782</v>
+        <v>1.886792452830</v>
       </c>
       <c r="I20" s="14">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="J20" s="14">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="K20" s="15">
-        <v>13.754646840148</v>
+        <v>10.264900662251</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.725388601036</v>
+        <v>-19.370460048426</v>
       </c>
       <c r="M20" s="15">
-        <v>-24.257425742574</v>
+        <v>-25.168539325842</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.648816936488</v>
+        <v>-93.620689655172</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D21" s="17">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.450704225352</v>
+        <v>-4.198473282442</v>
       </c>
       <c r="F21" s="17">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="G21" s="17">
-        <v>1022</v>
+        <v>1059</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.131115459882</v>
+        <v>-5.760151085930</v>
       </c>
       <c r="I21" s="17">
-        <v>2446</v>
+        <v>2697</v>
       </c>
       <c r="J21" s="17">
-        <v>2548</v>
+        <v>2810</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.003139717425</v>
+        <v>-4.021352313167</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.357810413885</v>
+        <v>-17.548150412717</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.829564077351</v>
+        <v>-19.203115638106</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.197087311946</v>
+        <v>-82.964881253158</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F22" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G22" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H22" s="15">
         <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J22" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>41.176470588235</v>
       </c>
       <c r="L22" s="15">
-        <v>12.5</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-8.163265306122</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G23" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H23" s="15">
-        <v>-23.076923076923</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="I23" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J23" s="14">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K23" s="15">
-        <v>5.617977528089</v>
+        <v>4.210526315789</v>
       </c>
       <c r="L23" s="15">
-        <v>-16.071428571428</v>
+        <v>-17.5</v>
       </c>
       <c r="M23" s="15">
-        <v>88</v>
+        <v>76.785714285714</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="D24" s="14">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="E24" s="15">
-        <v>-5.985915492957</v>
+        <v>-20.608108108108</v>
       </c>
       <c r="F24" s="14">
-        <v>856</v>
+        <v>923</v>
       </c>
       <c r="G24" s="14">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.647887323943</v>
+        <v>-19.458987783595</v>
       </c>
       <c r="I24" s="14">
-        <v>2303</v>
+        <v>2541</v>
       </c>
       <c r="J24" s="14">
-        <v>2817</v>
+        <v>3113</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.246361377351</v>
+        <v>-18.374558303886</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.353337828725</v>
+        <v>-22.695466991177</v>
       </c>
       <c r="M24" s="15">
-        <v>3.042505592841</v>
+        <v>4.096681687832</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D25" s="14">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="E25" s="15">
-        <v>-34.782608695652</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="G25" s="14">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="H25" s="15">
-        <v>-41.568627450980</v>
+        <v>-39.922480620155</v>
       </c>
       <c r="I25" s="14">
-        <v>876</v>
+        <v>950</v>
       </c>
       <c r="J25" s="14">
-        <v>1289</v>
+        <v>1424</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.040341349883</v>
+        <v>-33.286516853932</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.429608127721</v>
+        <v>-37.949052906597</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D26" s="14">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E26" s="15">
-        <v>-4.477611940298</v>
+        <v>8.196721311475</v>
       </c>
       <c r="F26" s="14">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="G26" s="14">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="H26" s="15">
-        <v>9.684210526315</v>
+        <v>3.012048192771</v>
       </c>
       <c r="I26" s="14">
-        <v>1241</v>
+        <v>1370</v>
       </c>
       <c r="J26" s="14">
-        <v>1135</v>
+        <v>1257</v>
       </c>
       <c r="K26" s="15">
-        <v>9.339207048458</v>
+        <v>8.989657915672</v>
       </c>
       <c r="L26" s="15">
-        <v>2.308326463314</v>
+        <v>2.621722846441</v>
       </c>
       <c r="M26" s="15">
-        <v>3.330557868442</v>
+        <v>3.085026335590</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D27" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>-30</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G27" s="14">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H27" s="15">
-        <v>-36.111111111111</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I27" s="14">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J27" s="14">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K27" s="15">
-        <v>-22.222222222222</v>
+        <v>-9.210526315789</v>
       </c>
       <c r="L27" s="15">
-        <v>-13.846153846153</v>
+        <v>2.985074626865</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D28" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E28" s="15">
-        <v>66.666666666666</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F28" s="14">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G28" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H28" s="15">
-        <v>18.181818181818</v>
+        <v>6.25</v>
       </c>
       <c r="I28" s="14">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="J28" s="14">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="K28" s="15">
-        <v>8.59375</v>
+        <v>5.633802816901</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.794520547945</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F29" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>466.666666666667</v>
+        <v>300</v>
       </c>
       <c r="I29" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J29" s="14">
+        <v>16</v>
+      </c>
+      <c r="K29" s="15">
+        <v>43.75</v>
+      </c>
+      <c r="L29" s="15">
         <v>15</v>
       </c>
-      <c r="K29" s="15">
-        <v>40</v>
-      </c>
-      <c r="L29" s="15">
-        <v>40</v>
-      </c>
       <c r="M29" s="15">
-        <v>-27.586206896551</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.328358208955</v>
+        <v>-85.064935064935</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
         <v>2</v>
@@ -1517,36 +1517,36 @@
         <v>100</v>
       </c>
       <c r="F30" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>300</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I30" s="14">
+        <v>17</v>
+      </c>
+      <c r="J30" s="14">
         <v>15</v>
       </c>
-      <c r="J30" s="14">
-        <v>14</v>
-      </c>
       <c r="K30" s="15">
-        <v>7.142857142857</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>7.142857142857</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M30" s="15">
-        <v>-40</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.603305785124</v>
+        <v>-87.591240875912</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="14">
         <v>2</v>
@@ -1558,36 +1558,36 @@
         <v>-33.333333333333</v>
       </c>
       <c r="F31" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H31" s="15">
-        <v>-45.454545454545</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I31" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J31" s="14">
+        <v>24</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
+      </c>
+      <c r="L31" s="15">
+        <v>-7.692307692307</v>
+      </c>
+      <c r="M31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K31" s="15">
-        <v>4.761904761904</v>
-      </c>
-      <c r="L31" s="15">
-        <v>-12</v>
-      </c>
-      <c r="M31" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,25 +1605,25 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="14">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>6</v>
@@ -1638,10 +1638,10 @@
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>446</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>15832</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>6359</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>24308</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>10688</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>32462</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>90355</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -861,31 +861,31 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
         <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="14">
         <v>9</v>
       </c>
       <c r="K14" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L14" s="15">
-        <v>-68.75</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="M14" s="15">
-        <v>-64.285714285714</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.566037735849</v>
+        <v>-89.285714285714</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>166.666666666667</v>
+        <v>150</v>
       </c>
       <c r="F15" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G15" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H15" s="15">
-        <v>4.166666666666</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I15" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J15" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K15" s="15">
-        <v>-11.111111111111</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L15" s="15">
-        <v>36.585365853658</v>
+        <v>30.434782608695</v>
       </c>
       <c r="M15" s="15">
-        <v>86.666666666666</v>
+        <v>81.818181818181</v>
       </c>
       <c r="N15" s="15">
-        <v>-52.136752136752</v>
+        <v>-51.612903225806</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E16" s="15">
-        <v>8.695652173913</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F16" s="14">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G16" s="14">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H16" s="15">
-        <v>1</v>
+        <v>-2.803738317757</v>
       </c>
       <c r="I16" s="14">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="J16" s="14">
-        <v>321</v>
+        <v>356</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.361370716510</v>
+        <v>-7.303370786516</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.845410628019</v>
+        <v>-24.311926605504</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.576214405360</v>
+        <v>-50.450450450450</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.559655596556</v>
+        <v>-90.646258503401</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D17" s="14">
         <v>68</v>
       </c>
       <c r="E17" s="15">
-        <v>-2.941176470588</v>
+        <v>1.470588235294</v>
       </c>
       <c r="F17" s="14">
         <v>261</v>
       </c>
       <c r="G17" s="14">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.434782608695</v>
+        <v>-7.773851590106</v>
       </c>
       <c r="I17" s="14">
-        <v>748</v>
+        <v>827</v>
       </c>
       <c r="J17" s="14">
-        <v>715</v>
+        <v>783</v>
       </c>
       <c r="K17" s="15">
-        <v>4.615384615384</v>
+        <v>5.619412515964</v>
       </c>
       <c r="L17" s="15">
-        <v>3.744798890429</v>
+        <v>6.709677419354</v>
       </c>
       <c r="M17" s="15">
-        <v>65.486725663716</v>
+        <v>67.748478701825</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.967897271268</v>
+        <v>-40.245664739884</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D18" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E18" s="15">
-        <v>-20.588235294117</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G18" s="14">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.008403361344</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="I18" s="14">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="J18" s="14">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.699386503067</v>
+        <v>-23.480662983425</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.776119402985</v>
+        <v>-23.268698060941</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.705882352941</v>
+        <v>-64.165588615782</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.984244449749</v>
+        <v>-93.904049295774</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>93</v>
       </c>
       <c r="D19" s="14">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.920792079207</v>
+        <v>-12.264150943396</v>
       </c>
       <c r="F19" s="14">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G19" s="14">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.800464037122</v>
+        <v>-1.210653753026</v>
       </c>
       <c r="I19" s="14">
-        <v>996</v>
+        <v>1097</v>
       </c>
       <c r="J19" s="14">
-        <v>1074</v>
+        <v>1180</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.262569832402</v>
+        <v>-7.033898305084</v>
       </c>
       <c r="L19" s="15">
-        <v>-25.169045830202</v>
+        <v>-23.340321453529</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.287292817679</v>
+        <v>-8.811305070656</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.247863247863</v>
+        <v>-43.801229508196</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D20" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E20" s="15">
-        <v>-6.060606060606</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="F20" s="14">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G20" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H20" s="15">
-        <v>1.886792452830</v>
+        <v>-1.754385964912</v>
       </c>
       <c r="I20" s="14">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="J20" s="14">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="K20" s="15">
-        <v>10.264900662251</v>
+        <v>5.899705014749</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.370460048426</v>
+        <v>-20.044543429844</v>
       </c>
       <c r="M20" s="15">
-        <v>-25.168539325842</v>
+        <v>-25.363825363825</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.620689655172</v>
+        <v>-93.708377146863</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D21" s="17">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.198473282442</v>
+        <v>-15.845070422535</v>
       </c>
       <c r="F21" s="17">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="17">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.760151085930</v>
+        <v>-5.926622765757</v>
       </c>
       <c r="I21" s="17">
-        <v>2697</v>
+        <v>2956</v>
       </c>
       <c r="J21" s="17">
-        <v>2810</v>
+        <v>3094</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.021352313167</v>
+        <v>-4.460245636716</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.548150412717</v>
+        <v>-15.903271692745</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.203115638106</v>
+        <v>-19.389146441232</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.964881253158</v>
+        <v>-82.907366716780</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="F22" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G22" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H22" s="15">
+        <v>-5.555555555555</v>
+      </c>
+      <c r="I22" s="14">
         <v>50</v>
       </c>
-      <c r="I22" s="14">
-        <v>48</v>
-      </c>
       <c r="J22" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K22" s="15">
-        <v>41.176470588235</v>
+        <v>31.578947368421</v>
       </c>
       <c r="L22" s="15">
-        <v>6.666666666666</v>
+        <v>6.382978723404</v>
       </c>
       <c r="M22" s="15">
-        <v>-11.111111111111</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G23" s="14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>-36.111111111111</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="I23" s="14">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J23" s="14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K23" s="15">
-        <v>4.210526315789</v>
+        <v>5</v>
       </c>
       <c r="L23" s="15">
-        <v>-17.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>76.785714285714</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="D24" s="14">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="E24" s="15">
-        <v>-20.608108108108</v>
+        <v>-6.474820143884</v>
       </c>
       <c r="F24" s="14">
-        <v>923</v>
+        <v>993</v>
       </c>
       <c r="G24" s="14">
-        <v>1146</v>
+        <v>1131</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.458987783595</v>
+        <v>-12.201591511936</v>
       </c>
       <c r="I24" s="14">
-        <v>2541</v>
+        <v>2786</v>
       </c>
       <c r="J24" s="14">
-        <v>3113</v>
+        <v>3391</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.374558303886</v>
+        <v>-17.841344736066</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.695466991177</v>
+        <v>-22.481914301613</v>
       </c>
       <c r="M24" s="15">
-        <v>4.096681687832</v>
+        <v>4.934086629001</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D25" s="14">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="E25" s="15">
-        <v>-46.666666666666</v>
+        <v>-31</v>
       </c>
       <c r="F25" s="14">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G25" s="14">
-        <v>516</v>
+        <v>476</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.922480620155</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>950</v>
+        <v>1017</v>
       </c>
       <c r="J25" s="14">
-        <v>1424</v>
+        <v>1524</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.286516853932</v>
+        <v>-33.267716535433</v>
       </c>
       <c r="L25" s="15">
-        <v>-37.949052906597</v>
+        <v>-39.679715302491</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>148</v>
+      </c>
+      <c r="D26" s="14">
         <v>132</v>
       </c>
-      <c r="D26" s="14">
-        <v>122</v>
-      </c>
       <c r="E26" s="15">
-        <v>8.196721311475</v>
+        <v>12.121212121212</v>
       </c>
       <c r="F26" s="14">
-        <v>513</v>
+        <v>542</v>
       </c>
       <c r="G26" s="14">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H26" s="15">
-        <v>3.012048192771</v>
+        <v>9.054325955734</v>
       </c>
       <c r="I26" s="14">
-        <v>1370</v>
+        <v>1510</v>
       </c>
       <c r="J26" s="14">
-        <v>1257</v>
+        <v>1389</v>
       </c>
       <c r="K26" s="15">
-        <v>8.989657915672</v>
+        <v>8.711303095752</v>
       </c>
       <c r="L26" s="15">
-        <v>2.621722846441</v>
+        <v>6.713780918727</v>
       </c>
       <c r="M26" s="15">
-        <v>3.085026335590</v>
+        <v>3.001364256480</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
         <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="F27" s="14">
         <v>31</v>
       </c>
       <c r="G27" s="14">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H27" s="15">
-        <v>6.896551724137</v>
+        <v>29.166666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J27" s="14">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K27" s="15">
-        <v>-9.210526315789</v>
+        <v>-3.75</v>
       </c>
       <c r="L27" s="15">
-        <v>2.985074626865</v>
+        <v>4.054054054054</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>7.142857142857</v>
+        <v>-18.75</v>
       </c>
       <c r="F28" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G28" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H28" s="15">
-        <v>6.25</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I28" s="14">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J28" s="14">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="K28" s="15">
-        <v>5.633802816901</v>
+        <v>2.531645569620</v>
       </c>
       <c r="L28" s="15">
-        <v>-5.660377358490</v>
+        <v>-4.705882352941</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F29" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I29" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J29" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K29" s="15">
-        <v>43.75</v>
+        <v>42.105263157894</v>
       </c>
       <c r="L29" s="15">
-        <v>15</v>
+        <v>17.391304347826</v>
       </c>
       <c r="M29" s="15">
-        <v>-34.285714285714</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.064935064935</v>
+        <v>-84.210526315789</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,75 +1508,75 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>166.666666666667</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I30" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J30" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K30" s="15">
-        <v>13.333333333333</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L30" s="15">
-        <v>-5.555555555555</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M30" s="15">
-        <v>-45.161290322580</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.591240875912</v>
+        <v>-86.928104575163</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>2</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E31" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G31" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H31" s="15">
-        <v>-42.857142857142</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="I31" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J31" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K31" s="15">
+        <v>-15.625</v>
+      </c>
+      <c r="L31" s="15">
         <v>0</v>
-      </c>
-      <c r="L31" s="15">
-        <v>-7.692307692307</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,32 +1610,32 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>3</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>3</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>6</v>
       </c>
       <c r="J33" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K33" s="15">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,369 +851,369 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="14">
         <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>6</v>
       </c>
       <c r="J14" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K14" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L14" s="15">
         <v>-64.705882352941</v>
       </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="N14" s="15">
-        <v>-89.285714285714</v>
+        <v>-90.322580645161</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E15" s="15">
-        <v>150</v>
+        <v>-20</v>
       </c>
       <c r="F15" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G15" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H15" s="15">
-        <v>21.052631578947</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J15" s="14">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K15" s="15">
-        <v>-7.692307692307</v>
+        <v>-8</v>
       </c>
       <c r="L15" s="15">
-        <v>30.434782608695</v>
+        <v>30.188679245283</v>
       </c>
       <c r="M15" s="15">
-        <v>81.818181818181</v>
+        <v>86.486486486486</v>
       </c>
       <c r="N15" s="15">
-        <v>-51.612903225806</v>
+        <v>-49.635036496350</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="14">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>20</v>
-      </c>
       <c r="D16" s="14">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E16" s="15">
-        <v>-42.857142857142</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F16" s="14">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G16" s="14">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H16" s="15">
-        <v>-2.803738317757</v>
+        <v>-9.734513274336</v>
       </c>
       <c r="I16" s="14">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="J16" s="14">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.303370786516</v>
+        <v>-6.084656084656</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.311926605504</v>
+        <v>-23.491379310344</v>
       </c>
       <c r="M16" s="15">
-        <v>-50.450450450450</v>
+        <v>-50.966850828729</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.646258503401</v>
+        <v>-90.672622175512</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D17" s="14">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="E17" s="15">
-        <v>1.470588235294</v>
+        <v>-46.464646464646</v>
       </c>
       <c r="F17" s="14">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G17" s="14">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.773851590106</v>
+        <v>-19.365079365079</v>
       </c>
       <c r="I17" s="14">
-        <v>827</v>
+        <v>882</v>
       </c>
       <c r="J17" s="14">
-        <v>783</v>
+        <v>882</v>
       </c>
       <c r="K17" s="15">
-        <v>5.619412515964</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>6.709677419354</v>
+        <v>3.642773207990</v>
       </c>
       <c r="M17" s="15">
-        <v>67.748478701825</v>
+        <v>66.101694915254</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.245664739884</v>
+        <v>-41.434262948207</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D18" s="14">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G18" s="14">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H18" s="15">
-        <v>-29.032258064516</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="I18" s="14">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="J18" s="14">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="K18" s="15">
-        <v>-23.480662983425</v>
+        <v>-22.631578947368</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.268698060941</v>
+        <v>-25.944584382871</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.165588615782</v>
+        <v>-63.837638376383</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.904049295774</v>
+        <v>-93.982808022922</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D19" s="14">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.264150943396</v>
+        <v>-23.728813559322</v>
       </c>
       <c r="F19" s="14">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="G19" s="14">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.210653753026</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="I19" s="14">
-        <v>1097</v>
+        <v>1185</v>
       </c>
       <c r="J19" s="14">
-        <v>1180</v>
+        <v>1298</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.033898305084</v>
+        <v>-8.705701078582</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.340321453529</v>
+        <v>-23.101881894873</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.811305070656</v>
+        <v>-7.058823529411</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.801229508196</v>
+        <v>-44.470477975632</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
         <v>27</v>
       </c>
       <c r="D20" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E20" s="15">
-        <v>-27.027027027027</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="F20" s="14">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G20" s="14">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="H20" s="15">
-        <v>-1.754385964912</v>
+        <v>-17.164179104477</v>
       </c>
       <c r="I20" s="14">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="J20" s="14">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="K20" s="15">
-        <v>5.899705014749</v>
+        <v>3.783783783783</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.044543429844</v>
+        <v>-22.424242424242</v>
       </c>
       <c r="M20" s="15">
-        <v>-25.363825363825</v>
+        <v>-25.146198830409</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.708377146863</v>
+        <v>-93.773309550835</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="D21" s="17">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.845070422535</v>
+        <v>-27.759197324414</v>
       </c>
       <c r="F21" s="17">
-        <v>1000</v>
+        <v>974</v>
       </c>
       <c r="G21" s="17">
-        <v>1063</v>
+        <v>1129</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.926622765757</v>
+        <v>-13.728963684676</v>
       </c>
       <c r="I21" s="17">
-        <v>2956</v>
+        <v>3175</v>
       </c>
       <c r="J21" s="17">
-        <v>3094</v>
+        <v>3393</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.460245636716</v>
+        <v>-6.424992631889</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.903271692745</v>
+        <v>-16.841278156102</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.389146441232</v>
+        <v>-18.839468302658</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.907366716780</v>
+        <v>-83.019574286019</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
         <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="F22" s="14">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="15">
-        <v>-5.555555555555</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I22" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J22" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K22" s="15">
-        <v>31.578947368421</v>
+        <v>18.604651162790</v>
       </c>
       <c r="L22" s="15">
-        <v>6.382978723404</v>
+        <v>4.081632653061</v>
       </c>
       <c r="M22" s="15">
-        <v>-16.666666666666</v>
+        <v>-17.741935483871</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
+        <v>-37.5</v>
+      </c>
+      <c r="F23" s="14">
         <v>20</v>
       </c>
-      <c r="F23" s="14">
-        <v>21</v>
-      </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H23" s="15">
-        <v>-32.258064516129</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="I23" s="14">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J23" s="14">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K23" s="15">
-        <v>5</v>
+        <v>0.925925925925</v>
       </c>
       <c r="L23" s="15">
-        <v>-16.666666666666</v>
+        <v>-19.852941176470</v>
       </c>
       <c r="M23" s="15">
-        <v>66.666666666666</v>
+        <v>55.714285714285</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="D24" s="14">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.474820143884</v>
+        <v>-10.441767068273</v>
       </c>
       <c r="F24" s="14">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="G24" s="14">
-        <v>1131</v>
+        <v>1107</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.201591511936</v>
+        <v>-12.104787714543</v>
       </c>
       <c r="I24" s="14">
-        <v>2786</v>
+        <v>3000</v>
       </c>
       <c r="J24" s="14">
-        <v>3391</v>
+        <v>3640</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.841344736066</v>
+        <v>-17.582417582417</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.481914301613</v>
+        <v>-22.037422037422</v>
       </c>
       <c r="M24" s="15">
-        <v>4.934086629001</v>
+        <v>5.300105300105</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D25" s="14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E25" s="15">
-        <v>-31</v>
+        <v>-38.181818181818</v>
       </c>
       <c r="F25" s="14">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="G25" s="14">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.714285714285</v>
+        <v>-38.260869565217</v>
       </c>
       <c r="I25" s="14">
-        <v>1017</v>
+        <v>1085</v>
       </c>
       <c r="J25" s="14">
-        <v>1524</v>
+        <v>1634</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.267716535433</v>
+        <v>-33.598531211750</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.679715302491</v>
+        <v>-39.889196675900</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="D26" s="14">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E26" s="15">
-        <v>12.121212121212</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F26" s="14">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="G26" s="14">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="H26" s="15">
-        <v>9.054325955734</v>
+        <v>-0.763358778625</v>
       </c>
       <c r="I26" s="14">
-        <v>1510</v>
+        <v>1630</v>
       </c>
       <c r="J26" s="14">
-        <v>1389</v>
+        <v>1525</v>
       </c>
       <c r="K26" s="15">
-        <v>8.711303095752</v>
+        <v>6.885245901639</v>
       </c>
       <c r="L26" s="15">
-        <v>6.713780918727</v>
+        <v>7.732980832782</v>
       </c>
       <c r="M26" s="15">
-        <v>3.001364256480</v>
+        <v>3.755569700827</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E27" s="15">
-        <v>75</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F27" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G27" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H27" s="15">
-        <v>29.166666666666</v>
+        <v>34.482758620689</v>
       </c>
       <c r="I27" s="14">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J27" s="14">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K27" s="15">
-        <v>-3.75</v>
+        <v>-1.098901098901</v>
       </c>
       <c r="L27" s="15">
-        <v>4.054054054054</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,163 +1426,163 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" s="15">
-        <v>-18.75</v>
+        <v>17.647058823529</v>
       </c>
       <c r="F28" s="14">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G28" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H28" s="15">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="J28" s="14">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="K28" s="15">
-        <v>2.531645569620</v>
+        <v>1.714285714285</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.705882352941</v>
+        <v>1.136363636363</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>4</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G29" s="14">
         <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I29" s="14">
         <v>27</v>
       </c>
       <c r="J29" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" s="15">
-        <v>42.105263157894</v>
+        <v>35</v>
       </c>
       <c r="L29" s="15">
         <v>17.391304347826</v>
       </c>
       <c r="M29" s="15">
-        <v>-30.769230769230</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.210526315789</v>
+        <v>-85.082872928176</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>3</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G30" s="14">
         <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>66.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>20</v>
       </c>
       <c r="J30" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30" s="15">
-        <v>11.111111111111</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L30" s="15">
         <v>-4.761904761904</v>
       </c>
       <c r="M30" s="15">
-        <v>-42.857142857142</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.928104575163</v>
+        <v>-87.730061349693</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>2</v>
       </c>
       <c r="D31" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F31" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G31" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H31" s="15">
-        <v>-47.368421052631</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I31" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J31" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K31" s="15">
-        <v>-15.625</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-9.375</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>3</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="E33" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
@@ -1626,22 +1626,22 @@
         <v>0</v>
       </c>
       <c r="I33" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="14">
         <v>8</v>
       </c>
       <c r="K33" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="L33" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>446</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>15832</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>6359</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>24308</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>10688</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>32462</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>90355</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -861,10 +861,10 @@
         <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>0</v>
@@ -873,19 +873,19 @@
         <v>6</v>
       </c>
       <c r="J14" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L14" s="15">
-        <v>-64.705882352941</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="M14" s="15">
         <v>-68.421052631578</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.322580645161</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G15" s="14">
         <v>24</v>
       </c>
       <c r="H15" s="15">
-        <v>16.666666666666</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J15" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K15" s="15">
-        <v>-8</v>
+        <v>-13.095238095238</v>
       </c>
       <c r="L15" s="15">
-        <v>30.188679245283</v>
+        <v>25.862068965517</v>
       </c>
       <c r="M15" s="15">
-        <v>86.486486486486</v>
+        <v>92.105263157894</v>
       </c>
       <c r="N15" s="15">
-        <v>-49.635036496350</v>
+        <v>-49.305555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D16" s="14">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E16" s="15">
-        <v>4.545454545454</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G16" s="14">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H16" s="15">
-        <v>-9.734513274336</v>
+        <v>-11.206896551724</v>
       </c>
       <c r="I16" s="14">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="J16" s="14">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.084656084656</v>
+        <v>-6.280193236714</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.491379310344</v>
+        <v>-22.088353413654</v>
       </c>
       <c r="M16" s="15">
-        <v>-50.966850828729</v>
+        <v>-48.677248677248</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.672622175512</v>
+        <v>-90.333831589437</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D17" s="14">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E17" s="15">
-        <v>-46.464646464646</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="F17" s="14">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G17" s="14">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H17" s="15">
-        <v>-19.365079365079</v>
+        <v>-16.293929712460</v>
       </c>
       <c r="I17" s="14">
-        <v>882</v>
+        <v>954</v>
       </c>
       <c r="J17" s="14">
-        <v>882</v>
+        <v>960</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-0.625</v>
       </c>
       <c r="L17" s="15">
-        <v>3.642773207990</v>
+        <v>5.298013245033</v>
       </c>
       <c r="M17" s="15">
-        <v>66.101694915254</v>
+        <v>62.798634812286</v>
       </c>
       <c r="N17" s="15">
-        <v>-41.434262948207</v>
+        <v>-42.006079027355</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D18" s="14">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E18" s="15">
-        <v>-16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F18" s="14">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G18" s="14">
         <v>116</v>
       </c>
       <c r="H18" s="15">
-        <v>-27.586206896551</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I18" s="14">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="J18" s="14">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.631578947368</v>
+        <v>-19.852941176470</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.944584382871</v>
+        <v>-22.511848341232</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.837638376383</v>
+        <v>-63.626251390433</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.982808022922</v>
+        <v>-93.780905287181</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D19" s="14">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E19" s="15">
-        <v>-23.728813559322</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="F19" s="14">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="G19" s="14">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.547169811320</v>
+        <v>-14.123006833713</v>
       </c>
       <c r="I19" s="14">
-        <v>1185</v>
+        <v>1288</v>
       </c>
       <c r="J19" s="14">
-        <v>1298</v>
+        <v>1412</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.705701078582</v>
+        <v>-8.781869688385</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.101881894873</v>
+        <v>-22.828040742959</v>
       </c>
       <c r="M19" s="15">
-        <v>-7.058823529411</v>
+        <v>-6.598984771573</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.470477975632</v>
+        <v>-44.097222222222</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D20" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E20" s="15">
-        <v>-12.903225806451</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F20" s="14">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G20" s="14">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H20" s="15">
-        <v>-17.164179104477</v>
+        <v>-17.266187050359</v>
       </c>
       <c r="I20" s="14">
-        <v>384</v>
+        <v>415</v>
       </c>
       <c r="J20" s="14">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="K20" s="15">
-        <v>3.783783783783</v>
+        <v>1.715686274509</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.424242424242</v>
+        <v>-21.401515151515</v>
       </c>
       <c r="M20" s="15">
-        <v>-25.146198830409</v>
+        <v>-24.954792043399</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.773309550835</v>
+        <v>-93.791143028126</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>216</v>
+        <v>272</v>
       </c>
       <c r="D21" s="17">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.759197324414</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>974</v>
+        <v>985</v>
       </c>
       <c r="G21" s="17">
-        <v>1129</v>
+        <v>1149</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.728963684676</v>
+        <v>-14.273281114012</v>
       </c>
       <c r="I21" s="17">
-        <v>3175</v>
+        <v>3451</v>
       </c>
       <c r="J21" s="17">
-        <v>3393</v>
+        <v>3697</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.424992631889</v>
+        <v>-6.654043819312</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.841278156102</v>
+        <v>-15.829268292682</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.839468302658</v>
+        <v>-18.416075650118</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.019574286019</v>
+        <v>-82.841089896579</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-80</v>
+        <v>50</v>
       </c>
       <c r="F22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H22" s="15">
-        <v>-57.894736842105</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J22" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K22" s="15">
-        <v>18.604651162790</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L22" s="15">
-        <v>4.081632653061</v>
+        <v>7.843137254901</v>
       </c>
       <c r="M22" s="15">
-        <v>-17.741935483871</v>
+        <v>-17.910447761194</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>29</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G23" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>-31.034482758620</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="I23" s="14">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J23" s="14">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="K23" s="15">
-        <v>0.925925925925</v>
+        <v>-2.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-19.852941176470</v>
+        <v>-18.75</v>
       </c>
       <c r="M23" s="15">
-        <v>55.714285714285</v>
+        <v>64.788732394366</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>29</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="D24" s="14">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.441767068273</v>
+        <v>-9.722222222222</v>
       </c>
       <c r="F24" s="14">
-        <v>973</v>
+        <v>964</v>
       </c>
       <c r="G24" s="14">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.104787714543</v>
+        <v>-13.231323132313</v>
       </c>
       <c r="I24" s="14">
-        <v>3000</v>
+        <v>3260</v>
       </c>
       <c r="J24" s="14">
-        <v>3640</v>
+        <v>3928</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.582417582417</v>
+        <v>-17.006109979633</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.037422037422</v>
+        <v>-20.835356969402</v>
       </c>
       <c r="M24" s="15">
-        <v>5.300105300105</v>
+        <v>6.535947712418</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>29</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D25" s="14">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E25" s="15">
-        <v>-38.181818181818</v>
+        <v>-37.815126050420</v>
       </c>
       <c r="F25" s="14">
         <v>284</v>
       </c>
       <c r="G25" s="14">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.260869565217</v>
+        <v>-38.793103448275</v>
       </c>
       <c r="I25" s="14">
-        <v>1085</v>
+        <v>1161</v>
       </c>
       <c r="J25" s="14">
-        <v>1634</v>
+        <v>1753</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.598531211750</v>
+        <v>-33.770678836280</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.889196675900</v>
+        <v>-40.308483290488</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>29</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="D26" s="14">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="E26" s="15">
-        <v>-11.764705882352</v>
+        <v>-23.770491803278</v>
       </c>
       <c r="F26" s="14">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="G26" s="14">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="H26" s="15">
-        <v>-0.763358778625</v>
+        <v>-4.296875</v>
       </c>
       <c r="I26" s="14">
-        <v>1630</v>
+        <v>1721</v>
       </c>
       <c r="J26" s="14">
-        <v>1525</v>
+        <v>1647</v>
       </c>
       <c r="K26" s="15">
-        <v>6.885245901639</v>
+        <v>4.493017607771</v>
       </c>
       <c r="L26" s="15">
-        <v>7.732980832782</v>
+        <v>5.582822085889</v>
       </c>
       <c r="M26" s="15">
-        <v>3.755569700827</v>
+        <v>0.058139534883</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>29</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D27" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" s="15">
-        <v>9.090909090909</v>
+        <v>-40</v>
       </c>
       <c r="F27" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G27" s="14">
         <v>29</v>
       </c>
       <c r="H27" s="15">
-        <v>34.482758620689</v>
+        <v>27.586206896551</v>
       </c>
       <c r="I27" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J27" s="14">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="K27" s="15">
-        <v>-1.098901098901</v>
+        <v>-6.930693069306</v>
       </c>
       <c r="L27" s="15">
-        <v>5.882352941176</v>
+        <v>1.075268817204</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>29</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D28" s="14">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>17.647058823529</v>
+        <v>216.666666666667</v>
       </c>
       <c r="F28" s="14">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G28" s="14">
         <v>53</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>16.981132075471</v>
       </c>
       <c r="I28" s="14">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="J28" s="14">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K28" s="15">
-        <v>1.714285714285</v>
+        <v>8.287292817679</v>
       </c>
       <c r="L28" s="15">
-        <v>1.136363636363</v>
+        <v>6.521739130434</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>29</v>
@@ -1466,117 +1466,117 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G29" s="14">
         <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J29" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" s="15">
-        <v>35</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>17.391304347826</v>
+        <v>3.703703703703</v>
       </c>
       <c r="M29" s="15">
-        <v>-34.146341463414</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.082872928176</v>
+        <v>-86.341463414634</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G30" s="14">
         <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
+        <v>21</v>
+      </c>
+      <c r="J30" s="14">
         <v>20</v>
       </c>
-      <c r="J30" s="14">
-        <v>19</v>
-      </c>
       <c r="K30" s="15">
-        <v>5.263157894736</v>
+        <v>5</v>
       </c>
       <c r="L30" s="15">
-        <v>-4.761904761904</v>
+        <v>-16</v>
       </c>
       <c r="M30" s="15">
-        <v>-45.945945945945</v>
+        <v>-51.162790697674</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.730061349693</v>
+        <v>-88.586956521739</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>2</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>9</v>
       </c>
       <c r="G31" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H31" s="15">
-        <v>-47.058823529411</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J31" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K31" s="15">
-        <v>-17.142857142857</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L31" s="15">
-        <v>-9.375</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>29</v>
@@ -1610,32 +1610,32 @@
       <c r="C33" s="14">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>29</v>
+      <c r="D33" s="14">
+        <v>2</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-50</v>
       </c>
       <c r="F33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I33" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J33" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K33" s="15">
-        <v>-12.5</v>
+        <v>-20</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>29</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,14 +851,14 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>2</v>
@@ -870,350 +870,350 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" s="14">
         <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>-45.454545454545</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L14" s="15">
-        <v>-68.421052631578</v>
+        <v>-65</v>
       </c>
       <c r="M14" s="15">
-        <v>-68.421052631578</v>
+        <v>-65</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.476190476190</v>
+        <v>-89.230769230769</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F15" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G15" s="14">
         <v>24</v>
       </c>
       <c r="H15" s="15">
-        <v>8.333333333333</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J15" s="14">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K15" s="15">
-        <v>-13.095238095238</v>
+        <v>-12.643678160919</v>
       </c>
       <c r="L15" s="15">
-        <v>25.862068965517</v>
+        <v>22.580645161290</v>
       </c>
       <c r="M15" s="15">
-        <v>92.105263157894</v>
+        <v>85.365853658536</v>
       </c>
       <c r="N15" s="15">
-        <v>-49.305555555555</v>
+        <v>-51.282051282051</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D16" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" s="15">
-        <v>-8.333333333333</v>
+        <v>-37.837837837837</v>
       </c>
       <c r="F16" s="14">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G16" s="14">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H16" s="15">
-        <v>-11.206896551724</v>
+        <v>-21.538461538461</v>
       </c>
       <c r="I16" s="14">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="J16" s="14">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.280193236714</v>
+        <v>-8.425720620842</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.088353413654</v>
+        <v>-20.576923076923</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.677248677248</v>
+        <v>-48.567870485678</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.333831589437</v>
+        <v>-90.300610615312</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D17" s="14">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E17" s="15">
-        <v>-11.538461538461</v>
+        <v>-4.938271604938</v>
       </c>
       <c r="F17" s="14">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="G17" s="14">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.293929712460</v>
+        <v>-17.177914110429</v>
       </c>
       <c r="I17" s="14">
-        <v>954</v>
+        <v>1035</v>
       </c>
       <c r="J17" s="14">
-        <v>960</v>
+        <v>1041</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.625</v>
+        <v>-0.576368876080</v>
       </c>
       <c r="L17" s="15">
-        <v>5.298013245033</v>
+        <v>5.504587155963</v>
       </c>
       <c r="M17" s="15">
-        <v>62.798634812286</v>
+        <v>65.6</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.006079027355</v>
+        <v>-42.016806722689</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D18" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E18" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G18" s="14">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H18" s="15">
-        <v>-13.793103448275</v>
+        <v>-6.730769230769</v>
       </c>
       <c r="I18" s="14">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="J18" s="14">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.852941176470</v>
+        <v>-18.139534883720</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.511848341232</v>
+        <v>-20.898876404494</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.626251390433</v>
+        <v>-64.044943820224</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.780905287181</v>
+        <v>-93.769911504424</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D19" s="14">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.280701754386</v>
+        <v>15.909090909090</v>
       </c>
       <c r="F19" s="14">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="G19" s="14">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.123006833713</v>
+        <v>-9.154929577464</v>
       </c>
       <c r="I19" s="14">
-        <v>1288</v>
+        <v>1398</v>
       </c>
       <c r="J19" s="14">
-        <v>1412</v>
+        <v>1500</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.781869688385</v>
+        <v>-6.8</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.828040742959</v>
+        <v>-22.419533851276</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.598984771573</v>
+        <v>-5.921938088829</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.097222222222</v>
+        <v>-43.583535108958</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D20" s="14">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E20" s="15">
-        <v>-15.789473684210</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="F20" s="14">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G20" s="14">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="H20" s="15">
-        <v>-17.266187050359</v>
+        <v>-16.774193548387</v>
       </c>
       <c r="I20" s="14">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="J20" s="14">
-        <v>408</v>
+        <v>457</v>
       </c>
       <c r="K20" s="15">
-        <v>1.715686274509</v>
+        <v>0.656455142231</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.401515151515</v>
+        <v>-20.138888888888</v>
       </c>
       <c r="M20" s="15">
-        <v>-24.954792043399</v>
+        <v>-23.588039867109</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.791143028126</v>
+        <v>-93.659545141281</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D21" s="17">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.526315789473</v>
+        <v>-2.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>985</v>
+        <v>1010</v>
       </c>
       <c r="G21" s="17">
-        <v>1149</v>
+        <v>1167</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.273281114012</v>
+        <v>-13.453299057412</v>
       </c>
       <c r="I21" s="17">
-        <v>3451</v>
+        <v>3741</v>
       </c>
       <c r="J21" s="17">
-        <v>3697</v>
+        <v>3977</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.654043819312</v>
+        <v>-5.934121196882</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.829268292682</v>
+        <v>-15.093054925102</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.416075650118</v>
+        <v>-17.888498683055</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.841089896579</v>
+        <v>-82.718159560216</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>5</v>
+      </c>
+      <c r="D22" s="14">
         <v>3</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
       <c r="E22" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I22" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J22" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K22" s="15">
-        <v>22.222222222222</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>7.843137254901</v>
+        <v>13.207547169811</v>
       </c>
       <c r="M22" s="15">
-        <v>-17.910447761194</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F23" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H23" s="15">
-        <v>-25.806451612903</v>
+        <v>-15.625</v>
       </c>
       <c r="I23" s="14">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J23" s="14">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="K23" s="15">
-        <v>-2.5</v>
+        <v>-1.574803149606</v>
       </c>
       <c r="L23" s="15">
-        <v>-18.75</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="M23" s="15">
-        <v>64.788732394366</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D24" s="14">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.722222222222</v>
+        <v>12.727272727272</v>
       </c>
       <c r="F24" s="14">
-        <v>964</v>
+        <v>981</v>
       </c>
       <c r="G24" s="14">
-        <v>1111</v>
+        <v>1035</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.231323132313</v>
+        <v>-5.217391304347</v>
       </c>
       <c r="I24" s="14">
-        <v>3260</v>
+        <v>3502</v>
       </c>
       <c r="J24" s="14">
-        <v>3928</v>
+        <v>4148</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.006109979633</v>
+        <v>-15.573770491803</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.835356969402</v>
+        <v>-20.318543799772</v>
       </c>
       <c r="M24" s="15">
-        <v>6.535947712418</v>
+        <v>6.056935190793</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D25" s="14">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E25" s="15">
-        <v>-37.815126050420</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G25" s="14">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.793103448275</v>
+        <v>-33.718244803695</v>
       </c>
       <c r="I25" s="14">
-        <v>1161</v>
+        <v>1235</v>
       </c>
       <c r="J25" s="14">
-        <v>1753</v>
+        <v>1857</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.770678836280</v>
+        <v>-33.494884221863</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.308483290488</v>
+        <v>-40.222652468538</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="D26" s="14">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E26" s="15">
-        <v>-23.770491803278</v>
+        <v>11.926605504587</v>
       </c>
       <c r="F26" s="14">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G26" s="14">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="H26" s="15">
-        <v>-4.296875</v>
+        <v>-3.406813627254</v>
       </c>
       <c r="I26" s="14">
-        <v>1721</v>
+        <v>1840</v>
       </c>
       <c r="J26" s="14">
-        <v>1647</v>
+        <v>1756</v>
       </c>
       <c r="K26" s="15">
-        <v>4.493017607771</v>
+        <v>4.783599088838</v>
       </c>
       <c r="L26" s="15">
-        <v>5.582822085889</v>
+        <v>4.486087450312</v>
       </c>
       <c r="M26" s="15">
-        <v>0.058139534883</v>
+        <v>0.877192982456</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-40</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G27" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H27" s="15">
-        <v>27.586206896551</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I27" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J27" s="14">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K27" s="15">
-        <v>-6.930693069306</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L27" s="15">
-        <v>1.075268817204</v>
+        <v>3.092783505154</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E28" s="15">
-        <v>216.666666666667</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>62</v>
       </c>
       <c r="G28" s="14">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H28" s="15">
-        <v>16.981132075471</v>
+        <v>29.166666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="J28" s="14">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="K28" s="15">
-        <v>8.287292817679</v>
+        <v>11.052631578947</v>
       </c>
       <c r="L28" s="15">
-        <v>6.521739130434</v>
+        <v>2.926829268292</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="15">
         <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J29" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K29" s="15">
-        <v>33.333333333333</v>
+        <v>29.166666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>3.703703703703</v>
+        <v>6.896551724137</v>
       </c>
       <c r="M29" s="15">
-        <v>-46.153846153846</v>
+        <v>-42.592592592592</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.341463414634</v>
+        <v>-85.377358490566</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G30" s="14">
         <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I30" s="14">
+        <v>24</v>
+      </c>
+      <c r="J30" s="14">
         <v>21</v>
       </c>
-      <c r="J30" s="14">
-        <v>20</v>
-      </c>
       <c r="K30" s="15">
-        <v>5</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L30" s="15">
-        <v>-16</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M30" s="15">
-        <v>-51.162790697674</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.586956521739</v>
+        <v>-87.368421052631</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,31 +1558,31 @@
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
         <v>18</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I31" s="14">
         <v>30</v>
       </c>
       <c r="J31" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K31" s="15">
-        <v>-23.076923076923</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="L31" s="15">
-        <v>-14.285714285714</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14">
-        <v>2</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-50</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>2</v>
@@ -1635,13 +1635,13 @@
         <v>-20</v>
       </c>
       <c r="L33" s="15">
-        <v>-46.666666666666</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>446</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>15832</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>6359</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>24308</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>10688</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>32462</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>90355</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,13 +861,13 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>7</v>
@@ -879,13 +879,13 @@
         <v>-36.363636363636</v>
       </c>
       <c r="L14" s="15">
-        <v>-65</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
-        <v>-65</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-89.230769230769</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14">
         <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H15" s="15">
-        <v>-4.166666666666</v>
+        <v>-4</v>
       </c>
       <c r="I15" s="14">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J15" s="14">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K15" s="15">
-        <v>-12.643678160919</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>22.580645161290</v>
+        <v>31.25</v>
       </c>
       <c r="M15" s="15">
-        <v>85.365853658536</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-51.282051282051</v>
+        <v>-49.700598802395</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D16" s="14">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E16" s="15">
-        <v>-37.837837837837</v>
+        <v>-15.625</v>
       </c>
       <c r="F16" s="14">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G16" s="14">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H16" s="15">
-        <v>-21.538461538461</v>
+        <v>-14.960629921259</v>
       </c>
       <c r="I16" s="14">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="J16" s="14">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.425720620842</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.576923076923</v>
+        <v>-19.378427787934</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.567870485678</v>
+        <v>-48.958333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.300610615312</v>
+        <v>-90.154052243804</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D17" s="14">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E17" s="15">
-        <v>-4.938271604938</v>
+        <v>-31</v>
       </c>
       <c r="F17" s="14">
         <v>270</v>
       </c>
       <c r="G17" s="14">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="H17" s="15">
-        <v>-17.177914110429</v>
+        <v>-24.581005586592</v>
       </c>
       <c r="I17" s="14">
-        <v>1035</v>
+        <v>1110</v>
       </c>
       <c r="J17" s="14">
-        <v>1041</v>
+        <v>1141</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.576368876080</v>
+        <v>-2.716914986853</v>
       </c>
       <c r="L17" s="15">
-        <v>5.504587155963</v>
+        <v>5.613701236917</v>
       </c>
       <c r="M17" s="15">
-        <v>65.6</v>
+        <v>65.919282511210</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.016806722689</v>
+        <v>-42.127215849843</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="14">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-34.375</v>
       </c>
       <c r="F18" s="14">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G18" s="14">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H18" s="15">
-        <v>-6.730769230769</v>
+        <v>-7</v>
       </c>
       <c r="I18" s="14">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="J18" s="14">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.139534883720</v>
+        <v>-19.264069264069</v>
       </c>
       <c r="L18" s="15">
-        <v>-20.898876404494</v>
+        <v>-19.612068965517</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.044943820224</v>
+        <v>-64.065510597302</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.769911504424</v>
+        <v>-93.794709698885</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D19" s="14">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="E19" s="15">
-        <v>15.909090909090</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="G19" s="14">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.154929577464</v>
+        <v>-9.713024282560</v>
       </c>
       <c r="I19" s="14">
-        <v>1398</v>
+        <v>1516</v>
       </c>
       <c r="J19" s="14">
-        <v>1500</v>
+        <v>1633</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.8</v>
+        <v>-7.164727495407</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.419533851276</v>
+        <v>-21.734641197728</v>
       </c>
       <c r="M19" s="15">
-        <v>-5.921938088829</v>
+        <v>-3.868103994927</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.583535108958</v>
+        <v>-42.575757575757</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D20" s="14">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E20" s="15">
-        <v>-10.204081632653</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="F20" s="14">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G20" s="14">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.774193548387</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="J20" s="14">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="K20" s="15">
-        <v>0.656455142231</v>
+        <v>-0.811359026369</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.138888888888</v>
+        <v>-19.306930693069</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.588039867109</v>
+        <v>-24.420401854714</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.659545141281</v>
+        <v>-93.706563706563</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D21" s="17">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.142857142857</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>1010</v>
+        <v>1037</v>
       </c>
       <c r="G21" s="17">
-        <v>1167</v>
+        <v>1219</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.453299057412</v>
+        <v>-14.930270713699</v>
       </c>
       <c r="I21" s="17">
-        <v>3741</v>
+        <v>4020</v>
       </c>
       <c r="J21" s="17">
-        <v>3977</v>
+        <v>4313</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.934121196882</v>
+        <v>-6.793415256202</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.093054925102</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.888498683055</v>
+        <v>-17.249897076986</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.718159560216</v>
+        <v>-82.563435263500</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15">
-        <v>66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F22" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G22" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H22" s="15">
-        <v>-28.571428571428</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I22" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J22" s="14">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="K22" s="15">
-        <v>25</v>
+        <v>15.789473684210</v>
       </c>
       <c r="L22" s="15">
-        <v>13.207547169811</v>
+        <v>17.857142857142</v>
       </c>
       <c r="M22" s="15">
-        <v>-18.918918918918</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15">
-        <v>14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="F23" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G23" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H23" s="15">
-        <v>-15.625</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I23" s="14">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J23" s="14">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="K23" s="15">
-        <v>-1.574803149606</v>
+        <v>-2.158273381294</v>
       </c>
       <c r="L23" s="15">
-        <v>-19.354838709677</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M23" s="15">
-        <v>66.666666666666</v>
+        <v>72.151898734177</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D24" s="14">
-        <v>220</v>
+        <v>277</v>
       </c>
       <c r="E24" s="15">
-        <v>12.727272727272</v>
+        <v>-10.830324909747</v>
       </c>
       <c r="F24" s="14">
-        <v>981</v>
+        <v>968</v>
       </c>
       <c r="G24" s="14">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.217391304347</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="I24" s="14">
-        <v>3502</v>
+        <v>3747</v>
       </c>
       <c r="J24" s="14">
-        <v>4148</v>
+        <v>4425</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.573770491803</v>
+        <v>-15.322033898305</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.318543799772</v>
+        <v>-20.072525597269</v>
       </c>
       <c r="M24" s="15">
-        <v>6.056935190793</v>
+        <v>4.899216125419</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D25" s="14">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>-29.457364341085</v>
       </c>
       <c r="F25" s="14">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="G25" s="14">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="H25" s="15">
-        <v>-33.718244803695</v>
+        <v>-33.116883116883</v>
       </c>
       <c r="I25" s="14">
-        <v>1235</v>
+        <v>1327</v>
       </c>
       <c r="J25" s="14">
-        <v>1857</v>
+        <v>1986</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.494884221863</v>
+        <v>-33.182275931520</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.222652468538</v>
+        <v>-40.305892937471</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D26" s="14">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="E26" s="15">
-        <v>11.926605504587</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="F26" s="14">
-        <v>482</v>
+        <v>447</v>
       </c>
       <c r="G26" s="14">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.406813627254</v>
+        <v>-12.007874015748</v>
       </c>
       <c r="I26" s="14">
-        <v>1840</v>
+        <v>1947</v>
       </c>
       <c r="J26" s="14">
-        <v>1756</v>
+        <v>1897</v>
       </c>
       <c r="K26" s="15">
-        <v>4.783599088838</v>
+        <v>2.635740643120</v>
       </c>
       <c r="L26" s="15">
-        <v>4.486087450312</v>
+        <v>4.173354735152</v>
       </c>
       <c r="M26" s="15">
-        <v>0.877192982456</v>
+        <v>0.360824742268</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,10 +1388,10 @@
         <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="F27" s="14">
         <v>32</v>
@@ -1403,16 +1403,16 @@
         <v>14.285714285714</v>
       </c>
       <c r="I27" s="14">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="J27" s="14">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K27" s="15">
-        <v>-3.846153846153</v>
+        <v>0.925925925925</v>
       </c>
       <c r="L27" s="15">
-        <v>3.092783505154</v>
+        <v>10.101010101010</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D28" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>31.25</v>
       </c>
       <c r="F28" s="14">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G28" s="14">
         <v>48</v>
       </c>
       <c r="H28" s="15">
-        <v>29.166666666666</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="J28" s="14">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="K28" s="15">
-        <v>11.052631578947</v>
+        <v>10.679611650485</v>
       </c>
       <c r="L28" s="15">
-        <v>2.926829268292</v>
+        <v>5.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,117 +1466,117 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>3</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>3</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>31</v>
       </c>
       <c r="J29" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K29" s="15">
-        <v>29.166666666666</v>
+        <v>14.814814814814</v>
       </c>
       <c r="L29" s="15">
-        <v>6.896551724137</v>
+        <v>-3.125</v>
       </c>
       <c r="M29" s="15">
-        <v>-42.592592592592</v>
+        <v>-44.642857142857</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.377358490566</v>
+        <v>-86.343612334801</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>3</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
       <c r="E30" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
         <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I30" s="14">
         <v>24</v>
       </c>
       <c r="J30" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K30" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="M30" s="15">
-        <v>-46.666666666666</v>
+        <v>-48.936170212766</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.368421052631</v>
+        <v>-88.177339901477</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G31" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H31" s="15">
-        <v>-77.777777777777</v>
+        <v>-56.25</v>
       </c>
       <c r="I31" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J31" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K31" s="15">
-        <v>-30.232558139534</v>
+        <v>-31.25</v>
       </c>
       <c r="L31" s="15">
-        <v>-18.918918918918</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1620,10 +1620,10 @@
         <v>2</v>
       </c>
       <c r="G33" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>8</v>
@@ -1635,7 +1635,7 @@
         <v>-20</v>
       </c>
       <c r="L33" s="15">
-        <v>-52.941176470588</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,366 +854,366 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I14" s="14">
         <v>7</v>
       </c>
       <c r="J14" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K14" s="15">
-        <v>-36.363636363636</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L14" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.181818181818</v>
       </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-72</v>
       </c>
       <c r="N14" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
+        <v>9</v>
+      </c>
+      <c r="D15" s="14">
         <v>6</v>
       </c>
-      <c r="D15" s="14">
-        <v>3</v>
-      </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F15" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H15" s="15">
-        <v>-4</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I15" s="14">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J15" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K15" s="15">
-        <v>-6.666666666666</v>
+        <v>-4.123711340206</v>
       </c>
       <c r="L15" s="15">
-        <v>31.25</v>
+        <v>34.782608695652</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>89.795918367346</v>
       </c>
       <c r="N15" s="15">
-        <v>-49.700598802395</v>
+        <v>-47.752808988764</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D16" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E16" s="15">
-        <v>-15.625</v>
+        <v>17.241379310344</v>
       </c>
       <c r="F16" s="14">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="G16" s="14">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.960629921259</v>
+        <v>-12.686567164179</v>
       </c>
       <c r="I16" s="14">
-        <v>441</v>
+        <v>476</v>
       </c>
       <c r="J16" s="14">
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.695652173913</v>
+        <v>-7.03125</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.378427787934</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.958333333333</v>
+        <v>-48.317046688382</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.154052243804</v>
+        <v>-89.940828402366</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" s="14">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E17" s="15">
-        <v>-31</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="F17" s="14">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G17" s="14">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="H17" s="15">
-        <v>-24.581005586592</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>1110</v>
+        <v>1178</v>
       </c>
       <c r="J17" s="14">
-        <v>1141</v>
+        <v>1218</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.716914986853</v>
+        <v>-3.284072249589</v>
       </c>
       <c r="L17" s="15">
-        <v>5.613701236917</v>
+        <v>4.618117229129</v>
       </c>
       <c r="M17" s="15">
-        <v>65.919282511210</v>
+        <v>63.838664812239</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.127215849843</v>
+        <v>-42.676399026764</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" s="15">
-        <v>-34.375</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F18" s="14">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G18" s="14">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="H18" s="15">
-        <v>-7</v>
+        <v>-11.206896551724</v>
       </c>
       <c r="I18" s="14">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="J18" s="14">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.264069264069</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.612068965517</v>
+        <v>-21.259842519685</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.065510597302</v>
+        <v>-63.768115942029</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.794709698885</v>
+        <v>-93.711680553372</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D19" s="14">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>-19.379844961240</v>
       </c>
       <c r="F19" s="14">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="G19" s="14">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.713024282560</v>
+        <v>-9.051724137931</v>
       </c>
       <c r="I19" s="14">
-        <v>1516</v>
+        <v>1631</v>
       </c>
       <c r="J19" s="14">
-        <v>1633</v>
+        <v>1762</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.164727495407</v>
+        <v>-7.434733257661</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.734641197728</v>
+        <v>-21.016949152542</v>
       </c>
       <c r="M19" s="15">
-        <v>-3.868103994927</v>
+        <v>-3.032104637336</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.575757575757</v>
+        <v>-41.645796064400</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D20" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E20" s="15">
-        <v>-19.444444444444</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F20" s="14">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G20" s="14">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="H20" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.969696969697</v>
       </c>
       <c r="I20" s="14">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="J20" s="14">
-        <v>493</v>
+        <v>535</v>
       </c>
       <c r="K20" s="15">
-        <v>-0.811359026369</v>
+        <v>-2.616822429906</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.306930693069</v>
+        <v>-19.349845201238</v>
       </c>
       <c r="M20" s="15">
-        <v>-24.420401854714</v>
+        <v>-23.042836041358</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.706563706563</v>
+        <v>-93.653307345596</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D21" s="17">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.833333333333</v>
+        <v>-15.360501567398</v>
       </c>
       <c r="F21" s="17">
-        <v>1037</v>
+        <v>1085</v>
       </c>
       <c r="G21" s="17">
-        <v>1219</v>
+        <v>1239</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.930270713699</v>
+        <v>-12.429378531073</v>
       </c>
       <c r="I21" s="17">
-        <v>4020</v>
+        <v>4306</v>
       </c>
       <c r="J21" s="17">
-        <v>4313</v>
+        <v>4633</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.793415256202</v>
+        <v>-7.058061731059</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.285714285714</v>
+        <v>-14.291401273885</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.249897076986</v>
+        <v>-16.824415684759</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.563435263500</v>
+        <v>-82.357520383496</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>11</v>
+      </c>
+      <c r="D22" s="14">
+        <v>4</v>
+      </c>
+      <c r="E22" s="15">
+        <v>175</v>
+      </c>
+      <c r="F22" s="14">
+        <v>25</v>
+      </c>
+      <c r="G22" s="14">
+        <v>18</v>
+      </c>
+      <c r="H22" s="15">
+        <v>38.888888888888</v>
+      </c>
+      <c r="I22" s="14">
+        <v>79</v>
+      </c>
+      <c r="J22" s="14">
+        <v>61</v>
+      </c>
+      <c r="K22" s="15">
+        <v>29.508196721311</v>
+      </c>
+      <c r="L22" s="15">
+        <v>25.396825396825</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-8.139534883720</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="14">
-        <v>4</v>
-      </c>
-      <c r="D22" s="14">
-        <v>9</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-55.555555555555</v>
-      </c>
-      <c r="F22" s="14">
-        <v>13</v>
-      </c>
-      <c r="G22" s="14">
-        <v>19</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-31.578947368421</v>
-      </c>
-      <c r="I22" s="14">
-        <v>66</v>
-      </c>
-      <c r="J22" s="14">
-        <v>57</v>
-      </c>
-      <c r="K22" s="15">
-        <v>15.789473684210</v>
-      </c>
-      <c r="L22" s="15">
-        <v>17.857142857142</v>
-      </c>
-      <c r="M22" s="15">
-        <v>-21.428571428571</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
         <v>12</v>
       </c>
       <c r="E23" s="15">
-        <v>-25</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G23" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H23" s="15">
-        <v>-15.384615384615</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="I23" s="14">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="J23" s="14">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="K23" s="15">
-        <v>-2.158273381294</v>
+        <v>-4.635761589403</v>
       </c>
       <c r="L23" s="15">
-        <v>-19.047619047619</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="15">
-        <v>72.151898734177</v>
+        <v>69.411764705882</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D24" s="14">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.830324909747</v>
+        <v>-4.494382022471</v>
       </c>
       <c r="F24" s="14">
-        <v>968</v>
+        <v>996</v>
       </c>
       <c r="G24" s="14">
-        <v>1034</v>
+        <v>1052</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.382978723404</v>
+        <v>-5.323193916349</v>
       </c>
       <c r="I24" s="14">
-        <v>3747</v>
+        <v>3991</v>
       </c>
       <c r="J24" s="14">
-        <v>4425</v>
+        <v>4692</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.322033898305</v>
+        <v>-14.940323955669</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.072525597269</v>
+        <v>-19.341147938561</v>
       </c>
       <c r="M24" s="15">
-        <v>4.899216125419</v>
+        <v>4.695697796432</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D25" s="14">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E25" s="15">
-        <v>-29.457364341085</v>
+        <v>-37.288135593220</v>
       </c>
       <c r="F25" s="14">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G25" s="14">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="H25" s="15">
-        <v>-33.116883116883</v>
+        <v>-34.042553191489</v>
       </c>
       <c r="I25" s="14">
-        <v>1327</v>
+        <v>1398</v>
       </c>
       <c r="J25" s="14">
-        <v>1986</v>
+        <v>2104</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.182275931520</v>
+        <v>-33.555133079847</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.305892937471</v>
+        <v>-40.561224489795</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="D26" s="14">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E26" s="15">
-        <v>-21.276595744680</v>
+        <v>13.385826771653</v>
       </c>
       <c r="F26" s="14">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="G26" s="14">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.007874015748</v>
+        <v>-5.010020040080</v>
       </c>
       <c r="I26" s="14">
-        <v>1947</v>
+        <v>2092</v>
       </c>
       <c r="J26" s="14">
-        <v>1897</v>
+        <v>2024</v>
       </c>
       <c r="K26" s="15">
-        <v>2.635740643120</v>
+        <v>3.359683794466</v>
       </c>
       <c r="L26" s="15">
-        <v>4.173354735152</v>
+        <v>5.284348263714</v>
       </c>
       <c r="M26" s="15">
-        <v>0.360824742268</v>
+        <v>0.625300625300</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>10</v>
+      </c>
+      <c r="D27" s="14">
         <v>7</v>
       </c>
-      <c r="D27" s="14">
-        <v>4</v>
-      </c>
       <c r="E27" s="15">
-        <v>75</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F27" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G27" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H27" s="15">
-        <v>14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="I27" s="14">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J27" s="14">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="K27" s="15">
-        <v>0.925925925925</v>
+        <v>2.586206896551</v>
       </c>
       <c r="L27" s="15">
-        <v>10.101010101010</v>
+        <v>11.214953271028</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,163 +1426,163 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28" s="15">
-        <v>31.25</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G28" s="14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>41.304347826087</v>
       </c>
       <c r="I28" s="14">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="J28" s="14">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="K28" s="15">
-        <v>10.679611650485</v>
+        <v>7.727272727272</v>
       </c>
       <c r="L28" s="15">
-        <v>5.555555555555</v>
+        <v>2.597402597402</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I29" s="14">
+        <v>32</v>
+      </c>
+      <c r="J29" s="14">
         <v>31</v>
       </c>
-      <c r="J29" s="14">
-        <v>27</v>
-      </c>
       <c r="K29" s="15">
-        <v>14.814814814814</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L29" s="15">
-        <v>-3.125</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="M29" s="15">
-        <v>-44.642857142857</v>
+        <v>-49.206349206349</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.343612334801</v>
+        <v>-86.885245901639</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I30" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J30" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L30" s="15">
-        <v>-20</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="M30" s="15">
-        <v>-48.936170212766</v>
+        <v>-51.923076923076</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.177339901477</v>
+        <v>-88.532110091743</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="14">
         <v>5</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-80</v>
-      </c>
-      <c r="F31" s="14">
-        <v>7</v>
       </c>
       <c r="G31" s="14">
         <v>16</v>
       </c>
       <c r="H31" s="15">
-        <v>-56.25</v>
+        <v>-68.75</v>
       </c>
       <c r="I31" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J31" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K31" s="15">
-        <v>-31.25</v>
+        <v>-31.372549019607</v>
       </c>
       <c r="L31" s="15">
-        <v>-13.157894736842</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
         <v>8</v>
@@ -1638,10 +1638,10 @@
         <v>-55.555555555555</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>446</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>15832</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>6359</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>24308</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>10688</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>32462</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>90355</v>

--- a/data/source/weekly/cs-en-us-pbbs.xlsx
+++ b/data/source/weekly/cs-en-us-pbbs.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>7</v>
@@ -885,335 +885,335 @@
         <v>-72</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.463414634146</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F15" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>19.047619047619</v>
+        <v>62.5</v>
       </c>
       <c r="I15" s="14">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J15" s="14">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K15" s="15">
-        <v>-4.123711340206</v>
+        <v>-1.980198019801</v>
       </c>
       <c r="L15" s="15">
-        <v>34.782608695652</v>
+        <v>35.616438356164</v>
       </c>
       <c r="M15" s="15">
-        <v>89.795918367346</v>
+        <v>90.384615384615</v>
       </c>
       <c r="N15" s="15">
-        <v>-47.752808988764</v>
+        <v>-47.058823529411</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="15">
-        <v>17.241379310344</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G16" s="14">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.686567164179</v>
+        <v>-10.9375</v>
       </c>
       <c r="I16" s="14">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="J16" s="14">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.03125</v>
+        <v>-6.642066420664</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.047619047619</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.317046688382</v>
+        <v>-48.049281314168</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.940828402366</v>
+        <v>-89.818913480885</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.987012987013</v>
+        <v>-26.506024096385</v>
       </c>
       <c r="F17" s="14">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G17" s="14">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>-19.648093841642</v>
       </c>
       <c r="I17" s="14">
-        <v>1178</v>
+        <v>1243</v>
       </c>
       <c r="J17" s="14">
-        <v>1218</v>
+        <v>1301</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.284072249589</v>
+        <v>-4.458109146810</v>
       </c>
       <c r="L17" s="15">
-        <v>4.618117229129</v>
+        <v>4.629629629629</v>
       </c>
       <c r="M17" s="15">
-        <v>63.838664812239</v>
+        <v>61.219195849546</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.676399026764</v>
+        <v>-43.653671804170</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E18" s="15">
-        <v>-29.411764705882</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="F18" s="14">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="G18" s="14">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H18" s="15">
-        <v>-11.206896551724</v>
+        <v>-26.050420168067</v>
       </c>
       <c r="I18" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="J18" s="14">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.354838709677</v>
+        <v>-20.303605313093</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.259842519685</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.768115942029</v>
+        <v>-64.194373401534</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.711680553372</v>
+        <v>-93.732278764363</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D19" s="14">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="E19" s="15">
-        <v>-19.379844961240</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="G19" s="14">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.051724137931</v>
+        <v>-2.654867256637</v>
       </c>
       <c r="I19" s="14">
-        <v>1631</v>
+        <v>1760</v>
       </c>
       <c r="J19" s="14">
-        <v>1762</v>
+        <v>1864</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.434733257661</v>
+        <v>-5.579399141630</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.016949152542</v>
+        <v>-18.744228993536</v>
       </c>
       <c r="M19" s="15">
-        <v>-3.032104637336</v>
+        <v>-0.621118012422</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.645796064400</v>
+        <v>-40.720781407881</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="14">
         <v>26</v>
       </c>
-      <c r="C20" s="14">
+      <c r="D20" s="14">
         <v>32</v>
       </c>
-      <c r="D20" s="14">
-        <v>42</v>
-      </c>
       <c r="E20" s="15">
-        <v>-23.809523809523</v>
+        <v>-18.75</v>
       </c>
       <c r="F20" s="14">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G20" s="14">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.969696969697</v>
+        <v>-16.352201257861</v>
       </c>
       <c r="I20" s="14">
-        <v>521</v>
+        <v>550</v>
       </c>
       <c r="J20" s="14">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="K20" s="15">
-        <v>-2.616822429906</v>
+        <v>-2.998236331569</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.349845201238</v>
+        <v>-19.472913616398</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.042836041358</v>
+        <v>-22.206506364922</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.653307345596</v>
+        <v>-93.642353485146</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D21" s="17">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.360501567398</v>
+        <v>-6.028368794326</v>
       </c>
       <c r="F21" s="17">
-        <v>1085</v>
+        <v>1076</v>
       </c>
       <c r="G21" s="17">
-        <v>1239</v>
+        <v>1217</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.429378531073</v>
+        <v>-11.585866885784</v>
       </c>
       <c r="I21" s="17">
-        <v>4306</v>
+        <v>4585</v>
       </c>
       <c r="J21" s="17">
-        <v>4633</v>
+        <v>4915</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.058061731059</v>
+        <v>-6.714140386571</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.291401273885</v>
+        <v>-13.245033112582</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.824415684759</v>
+        <v>-16.225105061209</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.357520383496</v>
+        <v>-82.205231700690</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E22" s="15">
-        <v>175</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F22" s="14">
         <v>25</v>
       </c>
       <c r="G22" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H22" s="15">
-        <v>38.888888888888</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I22" s="14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J22" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K22" s="15">
-        <v>29.508196721311</v>
+        <v>20.588235294117</v>
       </c>
       <c r="L22" s="15">
-        <v>25.396825396825</v>
+        <v>24.242424242424</v>
       </c>
       <c r="M22" s="15">
-        <v>-8.139534883720</v>
+        <v>-13.684210526315</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23" s="15">
-        <v>-41.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F23" s="14">
         <v>34</v>
       </c>
       <c r="G23" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H23" s="15">
-        <v>-20.930232558139</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="I23" s="14">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="J23" s="14">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K23" s="15">
-        <v>-4.635761589403</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="L23" s="15">
-        <v>-20</v>
+        <v>-17.297297297297</v>
       </c>
       <c r="M23" s="15">
-        <v>69.411764705882</v>
+        <v>70</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D24" s="14">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.494382022471</v>
+        <v>-2.371541501976</v>
       </c>
       <c r="F24" s="14">
-        <v>996</v>
+        <v>986</v>
       </c>
       <c r="G24" s="14">
-        <v>1052</v>
+        <v>1017</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.323193916349</v>
+        <v>-3.048180924287</v>
       </c>
       <c r="I24" s="14">
-        <v>3991</v>
+        <v>4226</v>
       </c>
       <c r="J24" s="14">
-        <v>4692</v>
+        <v>4945</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.940323955669</v>
+        <v>-14.539939332659</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.341147938561</v>
+        <v>-18.964525407478</v>
       </c>
       <c r="M24" s="15">
-        <v>4.695697796432</v>
+        <v>4.448838358872</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D25" s="14">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="E25" s="15">
-        <v>-37.288135593220</v>
+        <v>2.247191011235</v>
       </c>
       <c r="F25" s="14">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="G25" s="14">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.042553191489</v>
+        <v>-24.545454545454</v>
       </c>
       <c r="I25" s="14">
-        <v>1398</v>
+        <v>1489</v>
       </c>
       <c r="J25" s="14">
-        <v>2104</v>
+        <v>2193</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.555133079847</v>
+        <v>-32.102143182854</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.561224489795</v>
+        <v>-40.080482897384</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D26" s="14">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="E26" s="15">
-        <v>13.385826771653</v>
+        <v>32.038834951456</v>
       </c>
       <c r="F26" s="14">
-        <v>474</v>
+        <v>516</v>
       </c>
       <c r="G26" s="14">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.010020040080</v>
+        <v>7.5</v>
       </c>
       <c r="I26" s="14">
-        <v>2092</v>
+        <v>2229</v>
       </c>
       <c r="J26" s="14">
-        <v>2024</v>
+        <v>2127</v>
       </c>
       <c r="K26" s="15">
-        <v>3.359683794466</v>
+        <v>4.795486600846</v>
       </c>
       <c r="L26" s="15">
-        <v>5.284348263714</v>
+        <v>5.240793201133</v>
       </c>
       <c r="M26" s="15">
-        <v>0.625300625300</v>
+        <v>0.814111261872</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>42.857142857142</v>
+        <v>40</v>
       </c>
       <c r="F27" s="14">
         <v>30</v>
       </c>
       <c r="G27" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>25</v>
+        <v>57.894736842105</v>
       </c>
       <c r="I27" s="14">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J27" s="14">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K27" s="15">
-        <v>2.586206896551</v>
+        <v>3.305785123966</v>
       </c>
       <c r="L27" s="15">
-        <v>11.214953271028</v>
+        <v>6.837606837606</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,163 +1426,163 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D28" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E28" s="15">
-        <v>-26.666666666666</v>
+        <v>70</v>
       </c>
       <c r="F28" s="14">
         <v>65</v>
       </c>
       <c r="G28" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H28" s="15">
-        <v>41.304347826087</v>
+        <v>30</v>
       </c>
       <c r="I28" s="14">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="J28" s="14">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K28" s="15">
-        <v>7.727272727272</v>
+        <v>10</v>
       </c>
       <c r="L28" s="15">
-        <v>2.597402597402</v>
+        <v>2.845528455284</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
+        <v>3</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="14">
         <v>4</v>
       </c>
-      <c r="E29" s="15">
-        <v>-75</v>
-      </c>
-      <c r="F29" s="14">
-        <v>5</v>
-      </c>
       <c r="G29" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H29" s="15">
-        <v>-54.545454545454</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I29" s="14">
         <v>32</v>
       </c>
       <c r="J29" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K29" s="15">
-        <v>3.225806451612</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L29" s="15">
-        <v>-3.030303030303</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="M29" s="15">
-        <v>-49.206349206349</v>
+        <v>-50.769230769230</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.885245901639</v>
+        <v>-87.548638132295</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
+        <v>3</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="14">
         <v>4</v>
       </c>
-      <c r="E30" s="15">
-        <v>-75</v>
-      </c>
-      <c r="F30" s="14">
-        <v>5</v>
-      </c>
       <c r="G30" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H30" s="15">
-        <v>-44.444444444444</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I30" s="14">
         <v>25</v>
       </c>
       <c r="J30" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K30" s="15">
-        <v>-10.714285714285</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="L30" s="15">
-        <v>-19.354838709677</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M30" s="15">
-        <v>-51.923076923076</v>
+        <v>-53.703703703703</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.532110091743</v>
+        <v>-89.082969432314</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>5</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G31" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H31" s="15">
-        <v>-68.75</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I31" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J31" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K31" s="15">
-        <v>-31.372549019607</v>
+        <v>-21.153846153846</v>
       </c>
       <c r="L31" s="15">
-        <v>-7.894736842105</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,34 +1614,34 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="14">
-        <v>2</v>
-      </c>
-      <c r="H33" s="15">
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="14">
+        <v>9</v>
+      </c>
+      <c r="J33" s="14">
+        <v>8</v>
+      </c>
+      <c r="K33" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="L33" s="15">
         <v>-50</v>
       </c>
-      <c r="I33" s="14">
-        <v>8</v>
-      </c>
-      <c r="J33" s="14">
-        <v>10</v>
-      </c>
-      <c r="K33" s="15">
-        <v>-20</v>
-      </c>
-      <c r="L33" s="15">
-        <v>-55.555555555555</v>
-      </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>446</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>15832</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>6359</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>24308</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>10688</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>32462</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>90355</v>
